--- a/research/traditional_assets/database/data/chile/chile_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_chemical_specialty.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09686325136798529</v>
+        <v>0.09663457058929174</v>
       </c>
       <c r="C2">
-        <v>80.67410446145659</v>
+        <v>79.99561164333542</v>
       </c>
       <c r="D2">
-        <v>64.97410446145659</v>
+        <v>65.10511164333542</v>
       </c>
       <c r="E2">
-        <v>-3.45</v>
+        <v>-2.6405</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.8095</v>
       </c>
       <c r="G2">
         <v>15.7</v>
@@ -1451,28 +1451,28 @@
         <v>11.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04071785</v>
       </c>
       <c r="N2">
-        <v>11.5</v>
+        <v>11.45928215</v>
       </c>
       <c r="O2">
-        <v>3.105</v>
+        <v>3.0940061805</v>
       </c>
       <c r="P2">
-        <v>8.395</v>
+        <v>8.365275969500001</v>
       </c>
       <c r="Q2">
-        <v>8.695</v>
+        <v>8.665275969500001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09686325136798529</v>
+        <v>0.09723977837302196</v>
       </c>
       <c r="T2">
-        <v>0.9352413814778209</v>
+        <v>0.9421376058058898</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>282.4314152147031</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09663457058929174</v>
+        <v>0.09640588981059818</v>
       </c>
       <c r="C3">
-        <v>79.99561164333542</v>
+        <v>79.31764819171353</v>
       </c>
       <c r="D3">
-        <v>65.10511164333542</v>
+        <v>65.23664819171353</v>
       </c>
       <c r="E3">
-        <v>-2.6405</v>
+        <v>-1.831</v>
       </c>
       <c r="F3">
-        <v>0.8095</v>
+        <v>1.619</v>
       </c>
       <c r="G3">
         <v>15.7</v>
@@ -1533,28 +1533,28 @@
         <v>11.5</v>
       </c>
       <c r="M3">
-        <v>0.04071785</v>
+        <v>0.0814357</v>
       </c>
       <c r="N3">
-        <v>11.45928215</v>
+        <v>11.4185643</v>
       </c>
       <c r="O3">
-        <v>3.0940061805</v>
+        <v>3.083012361</v>
       </c>
       <c r="P3">
-        <v>8.365275969500001</v>
+        <v>8.335551939</v>
       </c>
       <c r="Q3">
-        <v>8.665275969500001</v>
+        <v>8.635551939000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09723977837302196</v>
+        <v>0.0976239896026512</v>
       </c>
       <c r="T3">
-        <v>0.9421376058058898</v>
+        <v>0.9491745694059599</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>282.4314152147031</v>
+        <v>141.2157076073516</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09640588981059818</v>
+        <v>0.09617720903190462</v>
       </c>
       <c r="C4">
-        <v>79.31764819171353</v>
+        <v>78.6402173216383</v>
       </c>
       <c r="D4">
-        <v>65.23664819171353</v>
+        <v>65.3687173216383</v>
       </c>
       <c r="E4">
-        <v>-1.831</v>
+        <v>-1.0215</v>
       </c>
       <c r="F4">
-        <v>1.619</v>
+        <v>2.4285</v>
       </c>
       <c r="G4">
         <v>15.7</v>
@@ -1615,28 +1615,28 @@
         <v>11.5</v>
       </c>
       <c r="M4">
-        <v>0.0814357</v>
+        <v>0.12215355</v>
       </c>
       <c r="N4">
-        <v>11.4185643</v>
+        <v>11.37784645</v>
       </c>
       <c r="O4">
-        <v>3.083012361</v>
+        <v>3.0720185415</v>
       </c>
       <c r="P4">
-        <v>8.335551939</v>
+        <v>8.3058279085</v>
       </c>
       <c r="Q4">
-        <v>8.635551939000001</v>
+        <v>8.6058279085</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0976239896026512</v>
+        <v>0.09801612271330373</v>
       </c>
       <c r="T4">
-        <v>0.9491745694059599</v>
+        <v>0.9563566250390212</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>141.2157076073516</v>
+        <v>94.14380507156771</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09617720903190462</v>
+        <v>0.09594852825321105</v>
       </c>
       <c r="C5">
-        <v>78.6402173216383</v>
+        <v>77.96332227424502</v>
       </c>
       <c r="D5">
-        <v>65.3687173216383</v>
+        <v>65.50132227424501</v>
       </c>
       <c r="E5">
-        <v>-1.0215</v>
+        <v>-0.2120000000000002</v>
       </c>
       <c r="F5">
-        <v>2.4285</v>
+        <v>3.238</v>
       </c>
       <c r="G5">
         <v>15.7</v>
@@ -1697,28 +1697,28 @@
         <v>11.5</v>
       </c>
       <c r="M5">
-        <v>0.12215355</v>
+        <v>0.1628714</v>
       </c>
       <c r="N5">
-        <v>11.37784645</v>
+        <v>11.3371286</v>
       </c>
       <c r="O5">
-        <v>3.0720185415</v>
+        <v>3.061024722</v>
       </c>
       <c r="P5">
-        <v>8.3058279085</v>
+        <v>8.276103878000001</v>
       </c>
       <c r="Q5">
-        <v>8.6058279085</v>
+        <v>8.576103878000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09801612271330373</v>
+        <v>0.09841642526376151</v>
       </c>
       <c r="T5">
-        <v>0.9563566250390212</v>
+        <v>0.9636883068311047</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>94.14380507156771</v>
+        <v>70.60785380367578</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09594852825321105</v>
+        <v>0.09571984747451749</v>
       </c>
       <c r="C6">
-        <v>77.96332227424502</v>
+        <v>77.28696631702181</v>
       </c>
       <c r="D6">
-        <v>65.50132227424501</v>
+        <v>65.6344663170218</v>
       </c>
       <c r="E6">
-        <v>-0.2120000000000002</v>
+        <v>0.5975000000000001</v>
       </c>
       <c r="F6">
-        <v>3.238</v>
+        <v>4.0475</v>
       </c>
       <c r="G6">
         <v>15.7</v>
@@ -1779,28 +1779,28 @@
         <v>11.5</v>
       </c>
       <c r="M6">
-        <v>0.1628714</v>
+        <v>0.20358925</v>
       </c>
       <c r="N6">
-        <v>11.3371286</v>
+        <v>11.29641075</v>
       </c>
       <c r="O6">
-        <v>3.061024722</v>
+        <v>3.0500309025</v>
       </c>
       <c r="P6">
-        <v>8.276103878000001</v>
+        <v>8.2463798475</v>
       </c>
       <c r="Q6">
-        <v>8.576103878000001</v>
+        <v>8.546379847500001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09841642526376151</v>
+        <v>0.0988251552363342</v>
       </c>
       <c r="T6">
-        <v>0.9636883068311047</v>
+        <v>0.9711743398188109</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>70.60785380367578</v>
+        <v>56.48628304294063</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09571984747451749</v>
+        <v>0.09549116669582394</v>
       </c>
       <c r="C7">
-        <v>77.28696631702181</v>
+        <v>76.6111527440781</v>
       </c>
       <c r="D7">
-        <v>65.6344663170218</v>
+        <v>65.76815274407809</v>
       </c>
       <c r="E7">
-        <v>0.5975000000000001</v>
+        <v>1.407</v>
       </c>
       <c r="F7">
-        <v>4.0475</v>
+        <v>4.857</v>
       </c>
       <c r="G7">
         <v>15.7</v>
@@ -1861,28 +1861,28 @@
         <v>11.5</v>
       </c>
       <c r="M7">
-        <v>0.20358925</v>
+        <v>0.2443071</v>
       </c>
       <c r="N7">
-        <v>11.29641075</v>
+        <v>11.2556929</v>
       </c>
       <c r="O7">
-        <v>3.0500309025</v>
+        <v>3.039037083</v>
       </c>
       <c r="P7">
-        <v>8.2463798475</v>
+        <v>8.216655816999999</v>
       </c>
       <c r="Q7">
-        <v>8.546379847500001</v>
+        <v>8.516655817</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0988251552363342</v>
+        <v>0.09924258159130206</v>
       </c>
       <c r="T7">
-        <v>0.9711743398188109</v>
+        <v>0.978819650104128</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>56.48628304294063</v>
+        <v>47.07190253578386</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09549116669582394</v>
+        <v>0.09526248591713038</v>
       </c>
       <c r="C8">
-        <v>76.6111527440781</v>
+        <v>75.93588487641635</v>
       </c>
       <c r="D8">
-        <v>65.76815274407809</v>
+        <v>65.90238487641635</v>
       </c>
       <c r="E8">
-        <v>1.407</v>
+        <v>2.216499999999999</v>
       </c>
       <c r="F8">
-        <v>4.857</v>
+        <v>5.666499999999999</v>
       </c>
       <c r="G8">
         <v>15.7</v>
@@ -1943,28 +1943,28 @@
         <v>11.5</v>
       </c>
       <c r="M8">
-        <v>0.2443071</v>
+        <v>0.2850249499999999</v>
       </c>
       <c r="N8">
-        <v>11.2556929</v>
+        <v>11.21497505</v>
       </c>
       <c r="O8">
-        <v>3.039037083</v>
+        <v>3.0280432635</v>
       </c>
       <c r="P8">
-        <v>8.216655816999999</v>
+        <v>8.186931786499999</v>
       </c>
       <c r="Q8">
-        <v>8.516655817</v>
+        <v>8.4869317865</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09924258159130206</v>
+        <v>0.09966898485712944</v>
       </c>
       <c r="T8">
-        <v>0.978819650104128</v>
+        <v>0.9866293756643979</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>47.07190253578386</v>
+        <v>40.34734503067188</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09526248591713037</v>
+        <v>0.09503380513843682</v>
       </c>
       <c r="C9">
-        <v>75.93588487641637</v>
+        <v>75.26116606220698</v>
       </c>
       <c r="D9">
-        <v>65.90238487641636</v>
+        <v>66.03716606220698</v>
       </c>
       <c r="E9">
-        <v>2.216500000000001</v>
+        <v>3.026</v>
       </c>
       <c r="F9">
-        <v>5.666500000000001</v>
+        <v>6.476</v>
       </c>
       <c r="G9">
         <v>15.7</v>
@@ -2025,28 +2025,28 @@
         <v>11.5</v>
       </c>
       <c r="M9">
-        <v>0.2850249500000001</v>
+        <v>0.3257428</v>
       </c>
       <c r="N9">
-        <v>11.21497505</v>
+        <v>11.1742572</v>
       </c>
       <c r="O9">
-        <v>3.0280432635</v>
+        <v>3.017049444</v>
       </c>
       <c r="P9">
-        <v>8.186931786499999</v>
+        <v>8.157207756</v>
       </c>
       <c r="Q9">
-        <v>8.4869317865</v>
+        <v>8.457207756000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09966898485712944</v>
+        <v>0.1001046577591704</v>
       </c>
       <c r="T9">
-        <v>0.9866293756643979</v>
+        <v>0.9946088778672826</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>40.34734503067187</v>
+        <v>35.30392690183789</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09503380513843682</v>
+        <v>0.09480512435974325</v>
       </c>
       <c r="C10">
-        <v>75.26116606220698</v>
+        <v>74.58699967706674</v>
       </c>
       <c r="D10">
-        <v>66.03716606220698</v>
+        <v>66.17249967706674</v>
       </c>
       <c r="E10">
-        <v>3.026</v>
+        <v>3.8355</v>
       </c>
       <c r="F10">
-        <v>6.476</v>
+        <v>7.2855</v>
       </c>
       <c r="G10">
         <v>15.7</v>
@@ -2107,28 +2107,28 @@
         <v>11.5</v>
       </c>
       <c r="M10">
-        <v>0.3257428</v>
+        <v>0.36646065</v>
       </c>
       <c r="N10">
-        <v>11.1742572</v>
+        <v>11.13353935</v>
       </c>
       <c r="O10">
-        <v>3.017049444</v>
+        <v>3.0060556245</v>
       </c>
       <c r="P10">
-        <v>8.157207756</v>
+        <v>8.127483725499999</v>
       </c>
       <c r="Q10">
-        <v>8.457207756000001</v>
+        <v>8.4274837255</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1001046577591704</v>
+        <v>0.1005499058898277</v>
       </c>
       <c r="T10">
-        <v>0.9946088778672826</v>
+        <v>1.002763753744956</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>35.30392690183789</v>
+        <v>31.38126835718924</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09480512435974325</v>
+        <v>0.0945764435810497</v>
       </c>
       <c r="C11">
-        <v>74.58699967706674</v>
+        <v>73.9133891243406</v>
       </c>
       <c r="D11">
-        <v>66.17249967706674</v>
+        <v>66.30838912434059</v>
       </c>
       <c r="E11">
-        <v>3.8355</v>
+        <v>4.644999999999999</v>
       </c>
       <c r="F11">
-        <v>7.2855</v>
+        <v>8.094999999999999</v>
       </c>
       <c r="G11">
         <v>15.7</v>
@@ -2189,28 +2189,28 @@
         <v>11.5</v>
       </c>
       <c r="M11">
-        <v>0.36646065</v>
+        <v>0.4071784999999999</v>
       </c>
       <c r="N11">
-        <v>11.13353935</v>
+        <v>11.0928215</v>
       </c>
       <c r="O11">
-        <v>3.0060556245</v>
+        <v>2.995061805</v>
       </c>
       <c r="P11">
-        <v>8.127483725499999</v>
+        <v>8.097759694999999</v>
       </c>
       <c r="Q11">
-        <v>8.4274837255</v>
+        <v>8.397759695</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1005499058898277</v>
+        <v>0.1010050484233885</v>
       </c>
       <c r="T11">
-        <v>1.002763753744956</v>
+        <v>1.011099849086577</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>31.38126835718924</v>
+        <v>28.24314152147032</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0945764435810497</v>
+        <v>0.09434776280235613</v>
       </c>
       <c r="C12">
-        <v>73.9133891243406</v>
+        <v>73.24033783538695</v>
       </c>
       <c r="D12">
-        <v>66.30838912434059</v>
+        <v>66.44483783538695</v>
       </c>
       <c r="E12">
-        <v>4.645</v>
+        <v>5.4545</v>
       </c>
       <c r="F12">
-        <v>8.095000000000001</v>
+        <v>8.904500000000001</v>
       </c>
       <c r="G12">
         <v>15.7</v>
@@ -2271,28 +2271,28 @@
         <v>11.5</v>
       </c>
       <c r="M12">
-        <v>0.4071785</v>
+        <v>0.44789635</v>
       </c>
       <c r="N12">
-        <v>11.0928215</v>
+        <v>11.05210365</v>
       </c>
       <c r="O12">
-        <v>2.995061805</v>
+        <v>2.9840679855</v>
       </c>
       <c r="P12">
-        <v>8.097759694999999</v>
+        <v>8.0680356645</v>
       </c>
       <c r="Q12">
-        <v>8.397759695</v>
+        <v>8.368035664500001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1010050484233885</v>
+        <v>0.1014704188790518</v>
       </c>
       <c r="T12">
-        <v>1.011099849086577</v>
+        <v>1.019623272413404</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.24314152147031</v>
+        <v>25.67558320133665</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09434776280235613</v>
+        <v>0.09411908202366256</v>
       </c>
       <c r="C13">
-        <v>73.24033783538695</v>
+        <v>72.56784926986654</v>
       </c>
       <c r="D13">
-        <v>66.44483783538695</v>
+        <v>66.58184926986654</v>
       </c>
       <c r="E13">
-        <v>5.4545</v>
+        <v>6.264</v>
       </c>
       <c r="F13">
-        <v>8.904500000000001</v>
+        <v>9.714</v>
       </c>
       <c r="G13">
         <v>15.7</v>
@@ -2353,28 +2353,28 @@
         <v>11.5</v>
       </c>
       <c r="M13">
-        <v>0.44789635</v>
+        <v>0.4886142</v>
       </c>
       <c r="N13">
-        <v>11.05210365</v>
+        <v>11.0113858</v>
       </c>
       <c r="O13">
-        <v>2.9840679855</v>
+        <v>2.973074166</v>
       </c>
       <c r="P13">
-        <v>8.0680356645</v>
+        <v>8.038311633999999</v>
       </c>
       <c r="Q13">
-        <v>8.368035664500001</v>
+        <v>8.338311634</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1014704188790518</v>
+        <v>0.1019463659359802</v>
       </c>
       <c r="T13">
-        <v>1.019623272413404</v>
+        <v>1.028340409906749</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>25.67558320133665</v>
+        <v>23.53595126789193</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09411908202366256</v>
+        <v>0.093890401244969</v>
       </c>
       <c r="C14">
-        <v>72.56784926986654</v>
+        <v>71.89592691603475</v>
       </c>
       <c r="D14">
-        <v>66.58184926986654</v>
+        <v>66.71942691603475</v>
       </c>
       <c r="E14">
-        <v>6.264</v>
+        <v>7.0735</v>
       </c>
       <c r="F14">
-        <v>9.714</v>
+        <v>10.5235</v>
       </c>
       <c r="G14">
         <v>15.7</v>
@@ -2435,28 +2435,28 @@
         <v>11.5</v>
       </c>
       <c r="M14">
-        <v>0.4886142</v>
+        <v>0.5293320499999999</v>
       </c>
       <c r="N14">
-        <v>11.0113858</v>
+        <v>10.97066795</v>
       </c>
       <c r="O14">
-        <v>2.973074166</v>
+        <v>2.9620803465</v>
       </c>
       <c r="P14">
-        <v>8.038311633999999</v>
+        <v>8.008587603499999</v>
       </c>
       <c r="Q14">
-        <v>8.338311634</v>
+        <v>8.308587603499999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1019463659359802</v>
+        <v>0.1024332543045621</v>
       </c>
       <c r="T14">
-        <v>1.028340409906749</v>
+        <v>1.037257941365459</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.53595126789193</v>
+        <v>21.72549347805409</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.093890401244969</v>
+        <v>0.09366172046627544</v>
       </c>
       <c r="C15">
-        <v>71.89592691603475</v>
+        <v>71.22457429103775</v>
       </c>
       <c r="D15">
-        <v>66.71942691603475</v>
+        <v>66.85757429103775</v>
       </c>
       <c r="E15">
-        <v>7.0735</v>
+        <v>7.883000000000002</v>
       </c>
       <c r="F15">
-        <v>10.5235</v>
+        <v>11.333</v>
       </c>
       <c r="G15">
         <v>15.7</v>
@@ -2517,28 +2517,28 @@
         <v>11.5</v>
       </c>
       <c r="M15">
-        <v>0.5293320499999999</v>
+        <v>0.5700499000000001</v>
       </c>
       <c r="N15">
-        <v>10.97066795</v>
+        <v>10.9299501</v>
       </c>
       <c r="O15">
-        <v>2.9620803465</v>
+        <v>2.951086527</v>
       </c>
       <c r="P15">
-        <v>8.008587603499999</v>
+        <v>7.978863572999999</v>
       </c>
       <c r="Q15">
-        <v>8.308587603499999</v>
+        <v>8.278863572999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1024332543045621</v>
+        <v>0.1029314656584598</v>
       </c>
       <c r="T15">
-        <v>1.037257941365459</v>
+        <v>1.046382857276697</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.72549347805409</v>
+        <v>20.17367251533593</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09366172046627544</v>
+        <v>0.09343303968758188</v>
       </c>
       <c r="C16">
-        <v>71.22457429103775</v>
+        <v>70.55379494121216</v>
       </c>
       <c r="D16">
-        <v>66.85757429103775</v>
+        <v>66.99629494121216</v>
       </c>
       <c r="E16">
-        <v>7.883000000000002</v>
+        <v>8.692500000000003</v>
       </c>
       <c r="F16">
-        <v>11.333</v>
+        <v>12.1425</v>
       </c>
       <c r="G16">
         <v>15.7</v>
@@ -2599,28 +2599,28 @@
         <v>11.5</v>
       </c>
       <c r="M16">
-        <v>0.5700499000000001</v>
+        <v>0.6107677500000001</v>
       </c>
       <c r="N16">
-        <v>10.9299501</v>
+        <v>10.88923225</v>
       </c>
       <c r="O16">
-        <v>2.951086527</v>
+        <v>2.9400927075</v>
       </c>
       <c r="P16">
-        <v>7.978863572999999</v>
+        <v>7.949139542499999</v>
       </c>
       <c r="Q16">
-        <v>8.278863572999999</v>
+        <v>8.2491395425</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1029314656584598</v>
+        <v>0.1034413996324493</v>
       </c>
       <c r="T16">
-        <v>1.046382857276697</v>
+        <v>1.055722477091728</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.17367251533593</v>
+        <v>18.82876101431354</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09343303968758188</v>
+        <v>0.09320435890888833</v>
       </c>
       <c r="C17">
-        <v>70.55379494121216</v>
+        <v>69.88359244238846</v>
       </c>
       <c r="D17">
-        <v>66.99629494121216</v>
+        <v>67.13559244238846</v>
       </c>
       <c r="E17">
-        <v>8.692499999999999</v>
+        <v>9.501999999999999</v>
       </c>
       <c r="F17">
-        <v>12.1425</v>
+        <v>12.952</v>
       </c>
       <c r="G17">
         <v>15.7</v>
@@ -2681,28 +2681,28 @@
         <v>11.5</v>
       </c>
       <c r="M17">
-        <v>0.6107677499999999</v>
+        <v>0.6514856</v>
       </c>
       <c r="N17">
-        <v>10.88923225</v>
+        <v>10.8485144</v>
       </c>
       <c r="O17">
-        <v>2.9400927075</v>
+        <v>2.929098888</v>
       </c>
       <c r="P17">
-        <v>7.949139542499999</v>
+        <v>7.919415511999999</v>
       </c>
       <c r="Q17">
-        <v>8.2491395425</v>
+        <v>8.219415511999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1034413996324493</v>
+        <v>0.1039634748915337</v>
       </c>
       <c r="T17">
-        <v>1.055722477091728</v>
+        <v>1.065284468807118</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.82876101431354</v>
+        <v>17.65196345091895</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09320435890888833</v>
+        <v>0.09297567813019476</v>
       </c>
       <c r="C18">
-        <v>69.88359244238846</v>
+        <v>69.21397040019841</v>
       </c>
       <c r="D18">
-        <v>67.13559244238846</v>
+        <v>67.2754704001984</v>
       </c>
       <c r="E18">
-        <v>9.501999999999999</v>
+        <v>10.3115</v>
       </c>
       <c r="F18">
-        <v>12.952</v>
+        <v>13.7615</v>
       </c>
       <c r="G18">
         <v>15.7</v>
@@ -2763,28 +2763,28 @@
         <v>11.5</v>
       </c>
       <c r="M18">
-        <v>0.6514856</v>
+        <v>0.6922034500000001</v>
       </c>
       <c r="N18">
-        <v>10.8485144</v>
+        <v>10.80779655</v>
       </c>
       <c r="O18">
-        <v>2.929098888</v>
+        <v>2.9181050685</v>
       </c>
       <c r="P18">
-        <v>7.919415511999999</v>
+        <v>7.889691481499999</v>
       </c>
       <c r="Q18">
-        <v>8.219415511999999</v>
+        <v>8.189691481499999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1039634748915337</v>
+        <v>0.1044981302773431</v>
       </c>
       <c r="T18">
-        <v>1.065284468807118</v>
+        <v>1.075076869961432</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.65196345091895</v>
+        <v>16.61361265968842</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09297567813019476</v>
+        <v>0.0927469973515012</v>
       </c>
       <c r="C19">
-        <v>69.21397040019841</v>
+        <v>68.54493245038594</v>
       </c>
       <c r="D19">
-        <v>67.2754704001984</v>
+        <v>67.41593245038594</v>
       </c>
       <c r="E19">
-        <v>10.3115</v>
+        <v>11.121</v>
       </c>
       <c r="F19">
-        <v>13.7615</v>
+        <v>14.571</v>
       </c>
       <c r="G19">
         <v>15.7</v>
@@ -2845,28 +2845,28 @@
         <v>11.5</v>
       </c>
       <c r="M19">
-        <v>0.6922034500000001</v>
+        <v>0.7329213</v>
       </c>
       <c r="N19">
-        <v>10.80779655</v>
+        <v>10.7670787</v>
       </c>
       <c r="O19">
-        <v>2.9181050685</v>
+        <v>2.907111249000001</v>
       </c>
       <c r="P19">
-        <v>7.889691481499999</v>
+        <v>7.859967451</v>
       </c>
       <c r="Q19">
-        <v>8.189691481499999</v>
+        <v>8.159967451</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1044981302773431</v>
+        <v>0.1050458260384161</v>
       </c>
       <c r="T19">
-        <v>1.075076869961432</v>
+        <v>1.085108110168291</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.61361265968842</v>
+        <v>15.69063417859462</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09274699735150121</v>
+        <v>0.09251831657280765</v>
       </c>
       <c r="C20">
-        <v>68.54493245038594</v>
+        <v>67.87648225912233</v>
       </c>
       <c r="D20">
-        <v>67.41593245038594</v>
+        <v>67.55698225912232</v>
       </c>
       <c r="E20">
-        <v>11.121</v>
+        <v>11.9305</v>
       </c>
       <c r="F20">
-        <v>14.571</v>
+        <v>15.3805</v>
       </c>
       <c r="G20">
         <v>15.7</v>
@@ -2927,28 +2927,28 @@
         <v>11.5</v>
       </c>
       <c r="M20">
-        <v>0.7329213</v>
+        <v>0.7736391500000001</v>
       </c>
       <c r="N20">
-        <v>10.7670787</v>
+        <v>10.72636085</v>
       </c>
       <c r="O20">
-        <v>2.907111249000001</v>
+        <v>2.8961174295</v>
       </c>
       <c r="P20">
-        <v>7.859967451</v>
+        <v>7.8302434205</v>
       </c>
       <c r="Q20">
-        <v>8.159967451</v>
+        <v>8.130243420500001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1050458260384161</v>
+        <v>0.1056070451516144</v>
       </c>
       <c r="T20">
-        <v>1.085108110168291</v>
+        <v>1.095387035318529</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.69063417859462</v>
+        <v>14.86481132708964</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09251831657280765</v>
+        <v>0.0922896357941141</v>
       </c>
       <c r="C21">
-        <v>67.87648225912233</v>
+        <v>67.20862352332512</v>
       </c>
       <c r="D21">
-        <v>67.55698225912232</v>
+        <v>67.69862352332511</v>
       </c>
       <c r="E21">
-        <v>11.9305</v>
+        <v>12.74</v>
       </c>
       <c r="F21">
-        <v>15.3805</v>
+        <v>16.19</v>
       </c>
       <c r="G21">
         <v>15.7</v>
@@ -3009,28 +3009,28 @@
         <v>11.5</v>
       </c>
       <c r="M21">
-        <v>0.7736391500000001</v>
+        <v>0.814357</v>
       </c>
       <c r="N21">
-        <v>10.72636085</v>
+        <v>10.685643</v>
       </c>
       <c r="O21">
-        <v>2.8961174295</v>
+        <v>2.88512361</v>
       </c>
       <c r="P21">
-        <v>7.8302434205</v>
+        <v>7.80051939</v>
       </c>
       <c r="Q21">
-        <v>8.130243420500001</v>
+        <v>8.100519390000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1056070451516144</v>
+        <v>0.1061822947426426</v>
       </c>
       <c r="T21">
-        <v>1.095387035318529</v>
+        <v>1.105922933597523</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.86481132708964</v>
+        <v>14.12157076073516</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0922896357941141</v>
+        <v>0.09206095501542054</v>
       </c>
       <c r="C22">
-        <v>67.20862352332512</v>
+        <v>66.54135997098108</v>
       </c>
       <c r="D22">
-        <v>67.69862352332511</v>
+        <v>67.84085997098107</v>
       </c>
       <c r="E22">
-        <v>12.74</v>
+        <v>13.5495</v>
       </c>
       <c r="F22">
-        <v>16.19</v>
+        <v>16.9995</v>
       </c>
       <c r="G22">
         <v>15.7</v>
@@ -3091,28 +3091,28 @@
         <v>11.5</v>
       </c>
       <c r="M22">
-        <v>0.814357</v>
+        <v>0.8550748500000001</v>
       </c>
       <c r="N22">
-        <v>10.685643</v>
+        <v>10.64492515</v>
       </c>
       <c r="O22">
-        <v>2.88512361</v>
+        <v>2.874129790500001</v>
       </c>
       <c r="P22">
-        <v>7.80051939</v>
+        <v>7.7707953595</v>
       </c>
       <c r="Q22">
-        <v>8.100519390000001</v>
+        <v>8.0707953595</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1061822947426426</v>
+        <v>0.1067721076144564</v>
       </c>
       <c r="T22">
-        <v>1.105922933597523</v>
+        <v>1.116725563478517</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.12157076073516</v>
+        <v>13.44911501022396</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09206095501542054</v>
+        <v>0.09207317423672698</v>
       </c>
       <c r="C23">
-        <v>66.54135997098108</v>
+        <v>65.7242446621911</v>
       </c>
       <c r="D23">
-        <v>67.84085997098107</v>
+        <v>67.83324466219109</v>
       </c>
       <c r="E23">
-        <v>13.5495</v>
+        <v>14.359</v>
       </c>
       <c r="F23">
-        <v>16.9995</v>
+        <v>17.809</v>
       </c>
       <c r="G23">
         <v>15.7</v>
@@ -3173,45 +3173,45 @@
         <v>11.5</v>
       </c>
       <c r="M23">
-        <v>0.8550748500000001</v>
+        <v>0.9225062000000001</v>
       </c>
       <c r="N23">
-        <v>10.64492515</v>
+        <v>10.5774938</v>
       </c>
       <c r="O23">
-        <v>2.874129790500001</v>
+        <v>2.855923326</v>
       </c>
       <c r="P23">
-        <v>7.7707953595</v>
+        <v>7.721570473999999</v>
       </c>
       <c r="Q23">
-        <v>8.0707953595</v>
+        <v>8.021570474000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1067721076144564</v>
+        <v>0.1073770438932397</v>
       </c>
       <c r="T23">
-        <v>1.116725563478517</v>
+        <v>1.12780518386928</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.27</v>
       </c>
       <c r="W23">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.44911501022396</v>
+        <v>12.46604087864125</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09207317423672698</v>
+        <v>0.09185544345803341</v>
       </c>
       <c r="C24">
-        <v>65.7242446621911</v>
+        <v>65.05069635003993</v>
       </c>
       <c r="D24">
-        <v>67.83324466219109</v>
+        <v>67.96919635003992</v>
       </c>
       <c r="E24">
-        <v>14.359</v>
+        <v>15.1685</v>
       </c>
       <c r="F24">
-        <v>17.809</v>
+        <v>18.6185</v>
       </c>
       <c r="G24">
         <v>15.7</v>
@@ -3255,28 +3255,28 @@
         <v>11.5</v>
       </c>
       <c r="M24">
-        <v>0.9225062000000001</v>
+        <v>0.9644383000000001</v>
       </c>
       <c r="N24">
-        <v>10.5774938</v>
+        <v>10.5355617</v>
       </c>
       <c r="O24">
-        <v>2.855923326</v>
+        <v>2.844601659</v>
       </c>
       <c r="P24">
-        <v>7.721570473999999</v>
+        <v>7.690960041</v>
       </c>
       <c r="Q24">
-        <v>8.021570474000001</v>
+        <v>7.990960041000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1073770438932397</v>
+        <v>0.1079976928026408</v>
       </c>
       <c r="T24">
-        <v>1.12780518386928</v>
+        <v>1.139172586607855</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.46604087864125</v>
+        <v>11.92403910130902</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09185544345803341</v>
+        <v>0.09163771267933984</v>
       </c>
       <c r="C25">
-        <v>65.05069635003993</v>
+        <v>64.37769408221688</v>
       </c>
       <c r="D25">
-        <v>67.96919635003992</v>
+        <v>68.10569408221687</v>
       </c>
       <c r="E25">
-        <v>15.1685</v>
+        <v>15.978</v>
       </c>
       <c r="F25">
-        <v>18.6185</v>
+        <v>19.428</v>
       </c>
       <c r="G25">
         <v>15.7</v>
@@ -3337,28 +3337,28 @@
         <v>11.5</v>
       </c>
       <c r="M25">
-        <v>0.9644383000000001</v>
+        <v>1.0063704</v>
       </c>
       <c r="N25">
-        <v>10.5355617</v>
+        <v>10.4936296</v>
       </c>
       <c r="O25">
-        <v>2.844601659</v>
+        <v>2.833279992</v>
       </c>
       <c r="P25">
-        <v>7.690960041</v>
+        <v>7.660349608000001</v>
       </c>
       <c r="Q25">
-        <v>7.990960041000001</v>
+        <v>7.960349608000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1079976928026408</v>
+        <v>0.1086346745780787</v>
       </c>
       <c r="T25">
-        <v>1.139172586607855</v>
+        <v>1.150839131523761</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.92403910130902</v>
+        <v>11.42720413875448</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09163771267933984</v>
+        <v>0.09141998190064629</v>
       </c>
       <c r="C26">
-        <v>64.37769408221688</v>
+        <v>63.70524115508847</v>
       </c>
       <c r="D26">
-        <v>68.10569408221687</v>
+        <v>68.24274115508847</v>
       </c>
       <c r="E26">
-        <v>15.978</v>
+        <v>16.7875</v>
       </c>
       <c r="F26">
-        <v>19.428</v>
+        <v>20.2375</v>
       </c>
       <c r="G26">
         <v>15.7</v>
@@ -3419,28 +3419,28 @@
         <v>11.5</v>
       </c>
       <c r="M26">
-        <v>1.0063704</v>
+        <v>1.0483025</v>
       </c>
       <c r="N26">
-        <v>10.4936296</v>
+        <v>10.4516975</v>
       </c>
       <c r="O26">
-        <v>2.833279992</v>
+        <v>2.821958325</v>
       </c>
       <c r="P26">
-        <v>7.660349608000001</v>
+        <v>7.629739174999999</v>
       </c>
       <c r="Q26">
-        <v>7.960349608000001</v>
+        <v>7.929739175</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1086346745780787</v>
+        <v>0.109288642534195</v>
       </c>
       <c r="T26">
-        <v>1.150839131523761</v>
+        <v>1.162816784304091</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.42720413875448</v>
+        <v>10.9701159732043</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09141998190064629</v>
+        <v>0.09120225112195274</v>
       </c>
       <c r="C27">
-        <v>63.70524115508847</v>
+        <v>63.03334089160747</v>
       </c>
       <c r="D27">
-        <v>68.24274115508847</v>
+        <v>68.38034089160746</v>
       </c>
       <c r="E27">
-        <v>16.7875</v>
+        <v>17.597</v>
       </c>
       <c r="F27">
-        <v>20.2375</v>
+        <v>21.047</v>
       </c>
       <c r="G27">
         <v>15.7</v>
@@ -3501,28 +3501,28 @@
         <v>11.5</v>
       </c>
       <c r="M27">
-        <v>1.0483025</v>
+        <v>1.0902346</v>
       </c>
       <c r="N27">
-        <v>10.4516975</v>
+        <v>10.4097654</v>
       </c>
       <c r="O27">
-        <v>2.821958325</v>
+        <v>2.810636658</v>
       </c>
       <c r="P27">
-        <v>7.629739174999999</v>
+        <v>7.599128742</v>
       </c>
       <c r="Q27">
-        <v>7.929739175</v>
+        <v>7.899128742</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.109288642534195</v>
+        <v>0.1099602852999361</v>
       </c>
       <c r="T27">
-        <v>1.162816784304091</v>
+        <v>1.175118157429835</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.9701159732043</v>
+        <v>10.54818843577336</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09120225112195274</v>
+        <v>0.09098452034325917</v>
       </c>
       <c r="C28">
-        <v>63.03334089160747</v>
+        <v>62.36199664158143</v>
       </c>
       <c r="D28">
-        <v>68.38034089160746</v>
+        <v>68.51849664158142</v>
       </c>
       <c r="E28">
-        <v>17.597</v>
+        <v>18.4065</v>
       </c>
       <c r="F28">
-        <v>21.047</v>
+        <v>21.8565</v>
       </c>
       <c r="G28">
         <v>15.7</v>
@@ -3583,28 +3583,28 @@
         <v>11.5</v>
       </c>
       <c r="M28">
-        <v>1.0902346</v>
+        <v>1.1321667</v>
       </c>
       <c r="N28">
-        <v>10.4097654</v>
+        <v>10.3678333</v>
       </c>
       <c r="O28">
-        <v>2.810636658</v>
+        <v>2.799314991000001</v>
       </c>
       <c r="P28">
-        <v>7.599128742</v>
+        <v>7.568518309</v>
       </c>
       <c r="Q28">
-        <v>7.899128742</v>
+        <v>7.868518309000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1099602852999361</v>
+        <v>0.1106503292373413</v>
       </c>
       <c r="T28">
-        <v>1.175118157429835</v>
+        <v>1.187756554476832</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.54818843577336</v>
+        <v>10.15751479000398</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09098452034325917</v>
+        <v>0.09111426956456559</v>
       </c>
       <c r="C29">
-        <v>62.36199664158143</v>
+        <v>61.47010030713789</v>
       </c>
       <c r="D29">
-        <v>68.51849664158142</v>
+        <v>68.43610030713789</v>
       </c>
       <c r="E29">
-        <v>18.4065</v>
+        <v>19.216</v>
       </c>
       <c r="F29">
-        <v>21.8565</v>
+        <v>22.666</v>
       </c>
       <c r="G29">
         <v>15.7</v>
@@ -3665,45 +3665,45 @@
         <v>11.5</v>
       </c>
       <c r="M29">
-        <v>1.1321667</v>
+        <v>1.212631</v>
       </c>
       <c r="N29">
-        <v>10.3678333</v>
+        <v>10.287369</v>
       </c>
       <c r="O29">
-        <v>2.799314991000001</v>
+        <v>2.77758963</v>
       </c>
       <c r="P29">
-        <v>7.568518309</v>
+        <v>7.50977937</v>
       </c>
       <c r="Q29">
-        <v>7.868518309000001</v>
+        <v>7.809779370000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1106503292373413</v>
+        <v>0.1113595410618967</v>
       </c>
       <c r="T29">
-        <v>1.187756554476832</v>
+        <v>1.200746018108469</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.27</v>
       </c>
       <c r="W29">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>10.15751479000398</v>
+        <v>9.483511472162593</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09111426956456559</v>
+        <v>0.09090894878587204</v>
       </c>
       <c r="C30">
-        <v>61.47010030713789</v>
+        <v>60.79107932904827</v>
       </c>
       <c r="D30">
-        <v>68.43610030713789</v>
+        <v>68.56657932904827</v>
       </c>
       <c r="E30">
-        <v>19.216</v>
+        <v>20.0255</v>
       </c>
       <c r="F30">
-        <v>22.666</v>
+        <v>23.4755</v>
       </c>
       <c r="G30">
         <v>15.7</v>
@@ -3747,28 +3747,28 @@
         <v>11.5</v>
       </c>
       <c r="M30">
-        <v>1.212631</v>
+        <v>1.25593925</v>
       </c>
       <c r="N30">
-        <v>10.287369</v>
+        <v>10.24406075</v>
       </c>
       <c r="O30">
-        <v>2.77758963</v>
+        <v>2.7658964025</v>
       </c>
       <c r="P30">
-        <v>7.50977937</v>
+        <v>7.478164347499999</v>
       </c>
       <c r="Q30">
-        <v>7.809779370000001</v>
+        <v>7.7781643475</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1113595410618967</v>
+        <v>0.1120887306843268</v>
       </c>
       <c r="T30">
-        <v>1.200746018108469</v>
+        <v>1.214101382124095</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.483511472162593</v>
+        <v>9.156493835191469</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09090894878587204</v>
+        <v>0.09070362800717849</v>
       </c>
       <c r="C31">
-        <v>60.79107932904827</v>
+        <v>60.11255683921887</v>
       </c>
       <c r="D31">
-        <v>68.56657932904827</v>
+        <v>68.69755683921886</v>
       </c>
       <c r="E31">
-        <v>20.0255</v>
+        <v>20.835</v>
       </c>
       <c r="F31">
-        <v>23.4755</v>
+        <v>24.285</v>
       </c>
       <c r="G31">
         <v>15.7</v>
@@ -3829,28 +3829,28 @@
         <v>11.5</v>
       </c>
       <c r="M31">
-        <v>1.25593925</v>
+        <v>1.2992475</v>
       </c>
       <c r="N31">
-        <v>10.24406075</v>
+        <v>10.2007525</v>
       </c>
       <c r="O31">
-        <v>2.7658964025</v>
+        <v>2.754203175</v>
       </c>
       <c r="P31">
-        <v>7.478164347499999</v>
+        <v>7.446549324999999</v>
       </c>
       <c r="Q31">
-        <v>7.7781643475</v>
+        <v>7.746549325</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1120887306843268</v>
+        <v>0.1128387542959693</v>
       </c>
       <c r="T31">
-        <v>1.214101382124095</v>
+        <v>1.227838327968739</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.156493835191471</v>
+        <v>8.851277374018423</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09070362800717849</v>
+        <v>0.09049830722848493</v>
       </c>
       <c r="C32">
-        <v>60.11255683921887</v>
+        <v>59.43453569978938</v>
       </c>
       <c r="D32">
-        <v>68.69755683921886</v>
+        <v>68.82903569978937</v>
       </c>
       <c r="E32">
-        <v>20.835</v>
+        <v>21.6445</v>
       </c>
       <c r="F32">
-        <v>24.285</v>
+        <v>25.0945</v>
       </c>
       <c r="G32">
         <v>15.7</v>
@@ -3911,28 +3911,28 @@
         <v>11.5</v>
       </c>
       <c r="M32">
-        <v>1.2992475</v>
+        <v>1.34255575</v>
       </c>
       <c r="N32">
-        <v>10.2007525</v>
+        <v>10.15744425</v>
       </c>
       <c r="O32">
-        <v>2.754203175</v>
+        <v>2.7425099475</v>
       </c>
       <c r="P32">
-        <v>7.446549324999999</v>
+        <v>7.414934302499999</v>
       </c>
       <c r="Q32">
-        <v>7.746549325</v>
+        <v>7.7149343025</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1128387542959693</v>
+        <v>0.1136105177224419</v>
       </c>
       <c r="T32">
-        <v>1.227838327968739</v>
+        <v>1.241973446156706</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.851277374018423</v>
+        <v>8.565752297437182</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09049830722848493</v>
+        <v>0.09029298644979135</v>
       </c>
       <c r="C33">
-        <v>59.43453569978938</v>
+        <v>58.75701879485273</v>
       </c>
       <c r="D33">
-        <v>68.82903569978937</v>
+        <v>68.96101879485272</v>
       </c>
       <c r="E33">
-        <v>21.6445</v>
+        <v>22.454</v>
       </c>
       <c r="F33">
-        <v>25.0945</v>
+        <v>25.904</v>
       </c>
       <c r="G33">
         <v>15.7</v>
@@ -3993,28 +3993,28 @@
         <v>11.5</v>
       </c>
       <c r="M33">
-        <v>1.34255575</v>
+        <v>1.385864</v>
       </c>
       <c r="N33">
-        <v>10.15744425</v>
+        <v>10.114136</v>
       </c>
       <c r="O33">
-        <v>2.7425099475</v>
+        <v>2.73081672</v>
       </c>
       <c r="P33">
-        <v>7.414934302499999</v>
+        <v>7.38331928</v>
       </c>
       <c r="Q33">
-        <v>7.7149343025</v>
+        <v>7.683319280000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1136105177224419</v>
+        <v>0.1144049800732226</v>
       </c>
       <c r="T33">
-        <v>1.241973446156706</v>
+        <v>1.256524303114908</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.565752297437182</v>
+        <v>8.298072538142272</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09029298644979135</v>
+        <v>0.09008766567109779</v>
       </c>
       <c r="C34">
-        <v>58.75701879485273</v>
+        <v>58.08000903066583</v>
       </c>
       <c r="D34">
-        <v>68.96101879485272</v>
+        <v>69.09350903066583</v>
       </c>
       <c r="E34">
-        <v>22.454</v>
+        <v>23.2635</v>
       </c>
       <c r="F34">
-        <v>25.904</v>
+        <v>26.7135</v>
       </c>
       <c r="G34">
         <v>15.7</v>
@@ -4075,28 +4075,28 @@
         <v>11.5</v>
       </c>
       <c r="M34">
-        <v>1.385864</v>
+        <v>1.42917225</v>
       </c>
       <c r="N34">
-        <v>10.114136</v>
+        <v>10.07082775</v>
       </c>
       <c r="O34">
-        <v>2.73081672</v>
+        <v>2.7191234925</v>
       </c>
       <c r="P34">
-        <v>7.38331928</v>
+        <v>7.3517042575</v>
       </c>
       <c r="Q34">
-        <v>7.683319280000001</v>
+        <v>7.6517042575</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1144049800732226</v>
+        <v>0.1152231577180564</v>
       </c>
       <c r="T34">
-        <v>1.256524303114908</v>
+        <v>1.27150951401216</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.298072538142272</v>
+        <v>8.0466157945622</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09008766567109779</v>
+        <v>0.08988234489240424</v>
       </c>
       <c r="C35">
-        <v>58.08000903066583</v>
+        <v>57.40350933586304</v>
       </c>
       <c r="D35">
-        <v>69.09350903066583</v>
+        <v>69.22650933586304</v>
       </c>
       <c r="E35">
-        <v>23.2635</v>
+        <v>24.073</v>
       </c>
       <c r="F35">
-        <v>26.7135</v>
+        <v>27.523</v>
       </c>
       <c r="G35">
         <v>15.7</v>
@@ -4157,28 +4157,28 @@
         <v>11.5</v>
       </c>
       <c r="M35">
-        <v>1.42917225</v>
+        <v>1.4724805</v>
       </c>
       <c r="N35">
-        <v>10.07082775</v>
+        <v>10.0275195</v>
       </c>
       <c r="O35">
-        <v>2.7191234925</v>
+        <v>2.707430265</v>
       </c>
       <c r="P35">
-        <v>7.3517042575</v>
+        <v>7.320089235</v>
       </c>
       <c r="Q35">
-        <v>7.6517042575</v>
+        <v>7.620089235000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1152231577180564</v>
+        <v>0.1160661286248549</v>
       </c>
       <c r="T35">
-        <v>1.27150951401216</v>
+        <v>1.286948822209329</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.0466157945622</v>
+        <v>7.809950624133902</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08988234489240424</v>
+        <v>0.08988142411371067</v>
       </c>
       <c r="C36">
-        <v>57.40350933586304</v>
+        <v>56.59460694045929</v>
       </c>
       <c r="D36">
-        <v>69.22650933586304</v>
+        <v>69.22710694045929</v>
       </c>
       <c r="E36">
-        <v>24.073</v>
+        <v>24.8825</v>
       </c>
       <c r="F36">
-        <v>27.523</v>
+        <v>28.3325</v>
       </c>
       <c r="G36">
         <v>15.7</v>
@@ -4239,45 +4239,45 @@
         <v>11.5</v>
       </c>
       <c r="M36">
-        <v>1.4724805</v>
+        <v>1.53845475</v>
       </c>
       <c r="N36">
-        <v>10.0275195</v>
+        <v>9.96154525</v>
       </c>
       <c r="O36">
-        <v>2.707430265</v>
+        <v>2.6896172175</v>
       </c>
       <c r="P36">
-        <v>7.320089235</v>
+        <v>7.2719280325</v>
       </c>
       <c r="Q36">
-        <v>7.620089235000001</v>
+        <v>7.571928032500001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1160661286248549</v>
+        <v>0.1169350370980164</v>
       </c>
       <c r="T36">
-        <v>1.286948822209329</v>
+        <v>1.302863186043334</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.27</v>
       </c>
       <c r="W36">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>7.809950624133902</v>
+        <v>7.47503298358304</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08988142411371067</v>
+        <v>0.08968194333501711</v>
       </c>
       <c r="C37">
-        <v>56.59460694045929</v>
+        <v>55.91481783314054</v>
       </c>
       <c r="D37">
-        <v>69.22710694045929</v>
+        <v>69.35681783314054</v>
       </c>
       <c r="E37">
-        <v>24.8825</v>
+        <v>25.692</v>
       </c>
       <c r="F37">
-        <v>28.3325</v>
+        <v>29.142</v>
       </c>
       <c r="G37">
         <v>15.7</v>
@@ -4321,28 +4321,28 @@
         <v>11.5</v>
       </c>
       <c r="M37">
-        <v>1.53845475</v>
+        <v>1.5824106</v>
       </c>
       <c r="N37">
-        <v>9.96154525</v>
+        <v>9.917589400000001</v>
       </c>
       <c r="O37">
-        <v>2.6896172175</v>
+        <v>2.677749138</v>
       </c>
       <c r="P37">
-        <v>7.2719280325</v>
+        <v>7.239840262</v>
       </c>
       <c r="Q37">
-        <v>7.571928032500001</v>
+        <v>7.539840262000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1169350370980164</v>
+        <v>0.1178310989609642</v>
       </c>
       <c r="T37">
-        <v>1.302863186043334</v>
+        <v>1.319274873747151</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.47503298358304</v>
+        <v>7.267393178483511</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08968194333501711</v>
+        <v>0.08948246255632356</v>
       </c>
       <c r="C38">
-        <v>55.91481783314055</v>
+        <v>55.23551571713094</v>
       </c>
       <c r="D38">
-        <v>69.35681783314054</v>
+        <v>69.48701571713093</v>
       </c>
       <c r="E38">
-        <v>25.692</v>
+        <v>26.5015</v>
       </c>
       <c r="F38">
-        <v>29.142</v>
+        <v>29.9515</v>
       </c>
       <c r="G38">
         <v>15.7</v>
@@ -4403,28 +4403,28 @@
         <v>11.5</v>
       </c>
       <c r="M38">
-        <v>1.5824106</v>
+        <v>1.62636645</v>
       </c>
       <c r="N38">
-        <v>9.917589400000001</v>
+        <v>9.873633550000001</v>
       </c>
       <c r="O38">
-        <v>2.677749138</v>
+        <v>2.665881058500001</v>
       </c>
       <c r="P38">
-        <v>7.239840262</v>
+        <v>7.207752491500001</v>
       </c>
       <c r="Q38">
-        <v>7.539840262000001</v>
+        <v>7.507752491500002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1178310989609642</v>
+        <v>0.1187556072322596</v>
       </c>
       <c r="T38">
-        <v>1.319274873747151</v>
+        <v>1.33620756740982</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.267393178483512</v>
+        <v>7.070977146632607</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08948246255632356</v>
+        <v>0.08928298177763</v>
       </c>
       <c r="C39">
-        <v>55.23551571713094</v>
+        <v>54.55670334015546</v>
       </c>
       <c r="D39">
-        <v>69.48701571713093</v>
+        <v>69.61770334015546</v>
       </c>
       <c r="E39">
-        <v>26.5015</v>
+        <v>27.311</v>
       </c>
       <c r="F39">
-        <v>29.9515</v>
+        <v>30.761</v>
       </c>
       <c r="G39">
         <v>15.7</v>
@@ -4485,28 +4485,28 @@
         <v>11.5</v>
       </c>
       <c r="M39">
-        <v>1.62636645</v>
+        <v>1.6703223</v>
       </c>
       <c r="N39">
-        <v>9.873633550000001</v>
+        <v>9.8296777</v>
       </c>
       <c r="O39">
-        <v>2.665881058500001</v>
+        <v>2.654012979</v>
       </c>
       <c r="P39">
-        <v>7.207752491500001</v>
+        <v>7.175664721</v>
       </c>
       <c r="Q39">
-        <v>7.507752491500002</v>
+        <v>7.475664721</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1187556072322596</v>
+        <v>0.1197099383510161</v>
       </c>
       <c r="T39">
-        <v>1.33620756740982</v>
+        <v>1.353686476997091</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.070977146632607</v>
+        <v>6.884898800668588</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08928298177763</v>
+        <v>0.08908350099893644</v>
       </c>
       <c r="C40">
-        <v>54.55670334015546</v>
+        <v>53.87838347064922</v>
       </c>
       <c r="D40">
-        <v>69.61770334015546</v>
+        <v>69.74888347064922</v>
       </c>
       <c r="E40">
-        <v>27.311</v>
+        <v>28.1205</v>
       </c>
       <c r="F40">
-        <v>30.761</v>
+        <v>31.5705</v>
       </c>
       <c r="G40">
         <v>15.7</v>
@@ -4567,28 +4567,28 @@
         <v>11.5</v>
       </c>
       <c r="M40">
-        <v>1.6703223</v>
+        <v>1.71427815</v>
       </c>
       <c r="N40">
-        <v>9.8296777</v>
+        <v>9.78572185</v>
       </c>
       <c r="O40">
-        <v>2.654012979</v>
+        <v>2.6421448995</v>
       </c>
       <c r="P40">
-        <v>7.175664721</v>
+        <v>7.1435769505</v>
       </c>
       <c r="Q40">
-        <v>7.475664721</v>
+        <v>7.443576950500001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1197099383510161</v>
+        <v>0.1206955590146499</v>
       </c>
       <c r="T40">
-        <v>1.353686476997091</v>
+        <v>1.371738465587224</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.884898800668588</v>
+        <v>6.708362933984779</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08908350099893644</v>
+        <v>0.08888402022024287</v>
       </c>
       <c r="C41">
-        <v>53.87838347064922</v>
+        <v>53.20055889795281</v>
       </c>
       <c r="D41">
-        <v>69.74888347064922</v>
+        <v>69.88055889795281</v>
       </c>
       <c r="E41">
-        <v>28.1205</v>
+        <v>28.93</v>
       </c>
       <c r="F41">
-        <v>31.5705</v>
+        <v>32.38</v>
       </c>
       <c r="G41">
         <v>15.7</v>
@@ -4649,28 +4649,28 @@
         <v>11.5</v>
       </c>
       <c r="M41">
-        <v>1.71427815</v>
+        <v>1.758234</v>
       </c>
       <c r="N41">
-        <v>9.78572185</v>
+        <v>9.741766</v>
       </c>
       <c r="O41">
-        <v>2.6421448995</v>
+        <v>2.63027682</v>
       </c>
       <c r="P41">
-        <v>7.1435769505</v>
+        <v>7.11148918</v>
       </c>
       <c r="Q41">
-        <v>7.443576950500001</v>
+        <v>7.41148918</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1206955590146499</v>
+        <v>0.1217140337004048</v>
       </c>
       <c r="T41">
-        <v>1.371738465587224</v>
+        <v>1.39039218713036</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.708362933984779</v>
+        <v>6.54065386063516</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08888402022024287</v>
+        <v>0.08868453944154933</v>
       </c>
       <c r="C42">
-        <v>53.20055889795281</v>
+        <v>52.52323243251013</v>
       </c>
       <c r="D42">
-        <v>69.88055889795281</v>
+        <v>70.01273243251013</v>
       </c>
       <c r="E42">
-        <v>28.93</v>
+        <v>29.7395</v>
       </c>
       <c r="F42">
-        <v>32.38</v>
+        <v>33.1895</v>
       </c>
       <c r="G42">
         <v>15.7</v>
@@ -4731,28 +4731,28 @@
         <v>11.5</v>
       </c>
       <c r="M42">
-        <v>1.758234</v>
+        <v>1.80218985</v>
       </c>
       <c r="N42">
-        <v>9.741766</v>
+        <v>9.69781015</v>
       </c>
       <c r="O42">
-        <v>2.63027682</v>
+        <v>2.6184087405</v>
       </c>
       <c r="P42">
-        <v>7.11148918</v>
+        <v>7.0794014095</v>
       </c>
       <c r="Q42">
-        <v>7.41148918</v>
+        <v>7.379401409500001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1217140337004048</v>
+        <v>0.1227670329517785</v>
       </c>
       <c r="T42">
-        <v>1.39039218713036</v>
+        <v>1.409678238217333</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.54065386063516</v>
+        <v>6.381125717692838</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08868453944154933</v>
+        <v>0.08848505866285578</v>
       </c>
       <c r="C43">
-        <v>52.52323243251013</v>
+        <v>51.8464069060683</v>
       </c>
       <c r="D43">
-        <v>70.01273243251013</v>
+        <v>70.1454069060683</v>
       </c>
       <c r="E43">
-        <v>29.7395</v>
+        <v>30.549</v>
       </c>
       <c r="F43">
-        <v>33.1895</v>
+        <v>33.999</v>
       </c>
       <c r="G43">
         <v>15.7</v>
@@ -4813,28 +4813,28 @@
         <v>11.5</v>
       </c>
       <c r="M43">
-        <v>1.80218985</v>
+        <v>1.8461457</v>
       </c>
       <c r="N43">
-        <v>9.69781015</v>
+        <v>9.653854299999999</v>
       </c>
       <c r="O43">
-        <v>2.6184087405</v>
+        <v>2.606540661</v>
       </c>
       <c r="P43">
-        <v>7.0794014095</v>
+        <v>7.047313638999999</v>
       </c>
       <c r="Q43">
-        <v>7.379401409500001</v>
+        <v>7.347313638999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1227670329517785</v>
+        <v>0.1238563425221651</v>
       </c>
       <c r="T43">
-        <v>1.409678238217333</v>
+        <v>1.429629325548683</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.381125717692838</v>
+        <v>6.229194152985865</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08848505866285578</v>
+        <v>0.0885994778841622</v>
       </c>
       <c r="C44">
-        <v>51.8464069060683</v>
+        <v>50.96074536575647</v>
       </c>
       <c r="D44">
-        <v>70.1454069060683</v>
+        <v>70.06924536575647</v>
       </c>
       <c r="E44">
-        <v>30.549</v>
+        <v>31.3585</v>
       </c>
       <c r="F44">
-        <v>33.999</v>
+        <v>34.8085</v>
       </c>
       <c r="G44">
         <v>15.7</v>
@@ -4895,45 +4895,45 @@
         <v>11.5</v>
       </c>
       <c r="M44">
-        <v>1.8461457</v>
+        <v>1.92491005</v>
       </c>
       <c r="N44">
-        <v>9.653854299999999</v>
+        <v>9.575089949999999</v>
       </c>
       <c r="O44">
-        <v>2.606540661</v>
+        <v>2.5852742865</v>
       </c>
       <c r="P44">
-        <v>7.047313638999999</v>
+        <v>6.989815663499999</v>
       </c>
       <c r="Q44">
-        <v>7.347313638999999</v>
+        <v>7.2898156635</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1238563425221651</v>
+        <v>0.1249838734809863</v>
       </c>
       <c r="T44">
-        <v>1.429629325548682</v>
+        <v>1.45028045103201</v>
       </c>
       <c r="U44">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.27</v>
       </c>
       <c r="W44">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>6.229194152985865</v>
+        <v>5.974305137011465</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0885994778841622</v>
+        <v>0.08840729710546864</v>
       </c>
       <c r="C45">
-        <v>50.96074536575647</v>
+        <v>50.27926235708727</v>
       </c>
       <c r="D45">
-        <v>70.06924536575647</v>
+        <v>70.19726235708727</v>
       </c>
       <c r="E45">
-        <v>31.3585</v>
+        <v>32.168</v>
       </c>
       <c r="F45">
-        <v>34.8085</v>
+        <v>35.618</v>
       </c>
       <c r="G45">
         <v>15.7</v>
@@ -4977,28 +4977,28 @@
         <v>11.5</v>
       </c>
       <c r="M45">
-        <v>1.92491005</v>
+        <v>1.9696754</v>
       </c>
       <c r="N45">
-        <v>9.575089949999999</v>
+        <v>9.5303246</v>
       </c>
       <c r="O45">
-        <v>2.5852742865</v>
+        <v>2.573187642</v>
       </c>
       <c r="P45">
-        <v>6.989815663499999</v>
+        <v>6.957136958</v>
       </c>
       <c r="Q45">
-        <v>7.2898156635</v>
+        <v>7.257136958</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1249838734809863</v>
+        <v>0.1261516734026226</v>
       </c>
       <c r="T45">
-        <v>1.45028045103201</v>
+        <v>1.471669116711171</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.974305137011465</v>
+        <v>5.838525474806661</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08840729710546864</v>
+        <v>0.08821511632677508</v>
       </c>
       <c r="C46">
-        <v>50.27926235708727</v>
+        <v>49.59824798045243</v>
       </c>
       <c r="D46">
-        <v>70.19726235708727</v>
+        <v>70.32574798045243</v>
       </c>
       <c r="E46">
-        <v>32.168</v>
+        <v>32.9775</v>
       </c>
       <c r="F46">
-        <v>35.618</v>
+        <v>36.4275</v>
       </c>
       <c r="G46">
         <v>15.7</v>
@@ -5059,28 +5059,28 @@
         <v>11.5</v>
       </c>
       <c r="M46">
-        <v>1.9696754</v>
+        <v>2.01444075</v>
       </c>
       <c r="N46">
-        <v>9.5303246</v>
+        <v>9.48555925</v>
       </c>
       <c r="O46">
-        <v>2.573187642</v>
+        <v>2.5611009975</v>
       </c>
       <c r="P46">
-        <v>6.957136958</v>
+        <v>6.924458252499999</v>
       </c>
       <c r="Q46">
-        <v>7.257136958</v>
+        <v>7.2244582525</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1261516734026226</v>
+        <v>0.1273619387759547</v>
       </c>
       <c r="T46">
-        <v>1.471669116711171</v>
+        <v>1.493835552051392</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.838525474806661</v>
+        <v>5.708780464255401</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08821511632677508</v>
+        <v>0.08802293554808152</v>
       </c>
       <c r="C47">
-        <v>49.59824798045243</v>
+        <v>48.91770481385382</v>
       </c>
       <c r="D47">
-        <v>70.32574798045243</v>
+        <v>70.45470481385382</v>
       </c>
       <c r="E47">
-        <v>32.9775</v>
+        <v>33.787</v>
       </c>
       <c r="F47">
-        <v>36.4275</v>
+        <v>37.237</v>
       </c>
       <c r="G47">
         <v>15.7</v>
@@ -5141,28 +5141,28 @@
         <v>11.5</v>
       </c>
       <c r="M47">
-        <v>2.01444075</v>
+        <v>2.0592061</v>
       </c>
       <c r="N47">
-        <v>9.48555925</v>
+        <v>9.440793899999999</v>
       </c>
       <c r="O47">
-        <v>2.5611009975</v>
+        <v>2.549014353</v>
       </c>
       <c r="P47">
-        <v>6.924458252499999</v>
+        <v>6.891779546999999</v>
       </c>
       <c r="Q47">
-        <v>7.2244582525</v>
+        <v>7.191779546999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1273619387759547</v>
+        <v>0.1286170287927436</v>
       </c>
       <c r="T47">
-        <v>1.493835552051392</v>
+        <v>1.516822966478288</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.708780464255401</v>
+        <v>5.584676541119413</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08802293554808152</v>
+        <v>0.08783075476938797</v>
       </c>
       <c r="C48">
-        <v>48.91770481385382</v>
+        <v>48.23763545423724</v>
       </c>
       <c r="D48">
-        <v>70.45470481385382</v>
+        <v>70.58413545423724</v>
       </c>
       <c r="E48">
-        <v>33.787</v>
+        <v>34.5965</v>
       </c>
       <c r="F48">
-        <v>37.237</v>
+        <v>38.0465</v>
       </c>
       <c r="G48">
         <v>15.7</v>
@@ -5223,28 +5223,28 @@
         <v>11.5</v>
       </c>
       <c r="M48">
-        <v>2.0592061</v>
+        <v>2.10397145</v>
       </c>
       <c r="N48">
-        <v>9.440793899999999</v>
+        <v>9.39602855</v>
       </c>
       <c r="O48">
-        <v>2.549014353</v>
+        <v>2.5369277085</v>
       </c>
       <c r="P48">
-        <v>6.891779546999999</v>
+        <v>6.8591008415</v>
       </c>
       <c r="Q48">
-        <v>7.191779546999999</v>
+        <v>7.159100841500001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1286170287927436</v>
+        <v>0.1299194806969584</v>
       </c>
       <c r="T48">
-        <v>1.516822966478288</v>
+        <v>1.540677830506199</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.584676541119413</v>
+        <v>5.465853635989215</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08783075476938797</v>
+        <v>0.0876385739906944</v>
       </c>
       <c r="C49">
-        <v>48.23763545423724</v>
+        <v>47.55804251766678</v>
       </c>
       <c r="D49">
-        <v>70.58413545423724</v>
+        <v>70.71404251766678</v>
       </c>
       <c r="E49">
-        <v>34.5965</v>
+        <v>35.406</v>
       </c>
       <c r="F49">
-        <v>38.0465</v>
+        <v>38.856</v>
       </c>
       <c r="G49">
         <v>15.7</v>
@@ -5305,28 +5305,28 @@
         <v>11.5</v>
       </c>
       <c r="M49">
-        <v>2.10397145</v>
+        <v>2.1487368</v>
       </c>
       <c r="N49">
-        <v>9.39602855</v>
+        <v>9.3512632</v>
       </c>
       <c r="O49">
-        <v>2.5369277085</v>
+        <v>2.524841064</v>
       </c>
       <c r="P49">
-        <v>6.8591008415</v>
+        <v>6.826422136</v>
       </c>
       <c r="Q49">
-        <v>7.159100841500001</v>
+        <v>7.126422136</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1299194806969584</v>
+        <v>0.1312720269051815</v>
       </c>
       <c r="T49">
-        <v>1.540677830506199</v>
+        <v>1.565450189304414</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.465853635989215</v>
+        <v>5.351981685239439</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0876385739906944</v>
+        <v>0.08744639321200083</v>
       </c>
       <c r="C50">
-        <v>47.55804251766678</v>
+        <v>46.87892863950102</v>
       </c>
       <c r="D50">
-        <v>70.71404251766678</v>
+        <v>70.84442863950102</v>
       </c>
       <c r="E50">
-        <v>35.406</v>
+        <v>36.2155</v>
       </c>
       <c r="F50">
-        <v>38.856</v>
+        <v>39.6655</v>
       </c>
       <c r="G50">
         <v>15.7</v>
@@ -5387,28 +5387,28 @@
         <v>11.5</v>
       </c>
       <c r="M50">
-        <v>2.1487368</v>
+        <v>2.19350215</v>
       </c>
       <c r="N50">
-        <v>9.3512632</v>
+        <v>9.30649785</v>
       </c>
       <c r="O50">
-        <v>2.524841064</v>
+        <v>2.5127544195</v>
       </c>
       <c r="P50">
-        <v>6.826422136</v>
+        <v>6.793743430499999</v>
       </c>
       <c r="Q50">
-        <v>7.126422136</v>
+        <v>7.0937434305</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1312720269051815</v>
+        <v>0.1326776141411781</v>
       </c>
       <c r="T50">
-        <v>1.565450189304414</v>
+        <v>1.591194013153539</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.351981685239439</v>
+        <v>5.242757569214144</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08744639321200083</v>
+        <v>0.08725421243330728</v>
       </c>
       <c r="C51">
-        <v>46.87892863950102</v>
+        <v>46.2002964745713</v>
       </c>
       <c r="D51">
-        <v>70.84442863950102</v>
+        <v>70.97529647457129</v>
       </c>
       <c r="E51">
-        <v>36.2155</v>
+        <v>37.025</v>
       </c>
       <c r="F51">
-        <v>39.6655</v>
+        <v>40.475</v>
       </c>
       <c r="G51">
         <v>15.7</v>
@@ -5469,28 +5469,28 @@
         <v>11.5</v>
       </c>
       <c r="M51">
-        <v>2.19350215</v>
+        <v>2.2382675</v>
       </c>
       <c r="N51">
-        <v>9.30649785</v>
+        <v>9.261732500000001</v>
       </c>
       <c r="O51">
-        <v>2.5127544195</v>
+        <v>2.500667775000001</v>
       </c>
       <c r="P51">
-        <v>6.793743430499999</v>
+        <v>6.761064725000001</v>
       </c>
       <c r="Q51">
-        <v>7.0937434305</v>
+        <v>7.061064725000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1326776141411781</v>
+        <v>0.1341394248666146</v>
       </c>
       <c r="T51">
-        <v>1.591194013153539</v>
+        <v>1.61796758995663</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.242757569214144</v>
+        <v>5.137902417829862</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08725421243330728</v>
+        <v>0.08706203165461374</v>
       </c>
       <c r="C52">
-        <v>46.2002964745713</v>
+        <v>45.52214869736186</v>
       </c>
       <c r="D52">
-        <v>70.97529647457129</v>
+        <v>71.10664869736186</v>
       </c>
       <c r="E52">
-        <v>37.025</v>
+        <v>37.8345</v>
       </c>
       <c r="F52">
-        <v>40.475</v>
+        <v>41.2845</v>
       </c>
       <c r="G52">
         <v>15.7</v>
@@ -5551,28 +5551,28 @@
         <v>11.5</v>
       </c>
       <c r="M52">
-        <v>2.2382675</v>
+        <v>2.28303285</v>
       </c>
       <c r="N52">
-        <v>9.261732500000001</v>
+        <v>9.21696715</v>
       </c>
       <c r="O52">
-        <v>2.500667775000001</v>
+        <v>2.4885811305</v>
       </c>
       <c r="P52">
-        <v>6.761064725000001</v>
+        <v>6.7283860195</v>
       </c>
       <c r="Q52">
-        <v>7.061064725000001</v>
+        <v>7.028386019500001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1341394248666146</v>
+        <v>0.1356609013359464</v>
       </c>
       <c r="T52">
-        <v>1.61796758995663</v>
+        <v>1.645833965812908</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.137902417829862</v>
+        <v>5.037159233166531</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08706203165461374</v>
+        <v>0.08686985087592017</v>
       </c>
       <c r="C53">
-        <v>45.52214869736186</v>
+        <v>44.8444880021921</v>
       </c>
       <c r="D53">
-        <v>71.10664869736186</v>
+        <v>71.2384880021921</v>
       </c>
       <c r="E53">
-        <v>37.8345</v>
+        <v>38.644</v>
       </c>
       <c r="F53">
-        <v>41.2845</v>
+        <v>42.094</v>
       </c>
       <c r="G53">
         <v>15.7</v>
@@ -5633,28 +5633,28 @@
         <v>11.5</v>
       </c>
       <c r="M53">
-        <v>2.28303285</v>
+        <v>2.3277982</v>
       </c>
       <c r="N53">
-        <v>9.21696715</v>
+        <v>9.1722018</v>
       </c>
       <c r="O53">
-        <v>2.4885811305</v>
+        <v>2.476494486</v>
       </c>
       <c r="P53">
-        <v>6.7283860195</v>
+        <v>6.695707314</v>
       </c>
       <c r="Q53">
-        <v>7.028386019500001</v>
+        <v>6.995707314000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1356609013359464</v>
+        <v>0.137245772658167</v>
       </c>
       <c r="T53">
-        <v>1.645833965812908</v>
+        <v>1.674861440663198</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.037159233166531</v>
+        <v>4.940290786374867</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08686985087592017</v>
+        <v>0.08667767009722659</v>
       </c>
       <c r="C54">
-        <v>44.8444880021921</v>
+        <v>44.16731710340073</v>
       </c>
       <c r="D54">
-        <v>71.2384880021921</v>
+        <v>71.37081710340073</v>
       </c>
       <c r="E54">
-        <v>38.644</v>
+        <v>39.4535</v>
       </c>
       <c r="F54">
-        <v>42.094</v>
+        <v>42.9035</v>
       </c>
       <c r="G54">
         <v>15.7</v>
@@ -5715,28 +5715,28 @@
         <v>11.5</v>
       </c>
       <c r="M54">
-        <v>2.3277982</v>
+        <v>2.37256355</v>
       </c>
       <c r="N54">
-        <v>9.1722018</v>
+        <v>9.127436449999999</v>
       </c>
       <c r="O54">
-        <v>2.476494486</v>
+        <v>2.4644078415</v>
       </c>
       <c r="P54">
-        <v>6.695707314</v>
+        <v>6.663028608499999</v>
       </c>
       <c r="Q54">
-        <v>6.995707314000001</v>
+        <v>6.9630286085</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.137245772658167</v>
+        <v>0.1388980853132481</v>
       </c>
       <c r="T54">
-        <v>1.674861440663198</v>
+        <v>1.705124127209244</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.940290786374867</v>
+        <v>4.84707775266968</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08667767009722659</v>
+        <v>0.08648548931853303</v>
       </c>
       <c r="C55">
-        <v>44.16731710340073</v>
+        <v>43.49063873553204</v>
       </c>
       <c r="D55">
-        <v>71.37081710340073</v>
+        <v>71.50363873553204</v>
       </c>
       <c r="E55">
-        <v>39.4535</v>
+        <v>40.263</v>
       </c>
       <c r="F55">
-        <v>42.9035</v>
+        <v>43.713</v>
       </c>
       <c r="G55">
         <v>15.7</v>
@@ -5797,28 +5797,28 @@
         <v>11.5</v>
       </c>
       <c r="M55">
-        <v>2.37256355</v>
+        <v>2.4173289</v>
       </c>
       <c r="N55">
-        <v>9.127436449999999</v>
+        <v>9.082671099999999</v>
       </c>
       <c r="O55">
-        <v>2.4644078415</v>
+        <v>2.452321197</v>
       </c>
       <c r="P55">
-        <v>6.663028608499999</v>
+        <v>6.630349902999999</v>
       </c>
       <c r="Q55">
-        <v>6.9630286085</v>
+        <v>6.930349903</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1388980853132481</v>
+        <v>0.1406222376489848</v>
       </c>
       <c r="T55">
-        <v>1.705124127209244</v>
+        <v>1.736702582735553</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.84707775266968</v>
+        <v>4.757317053546167</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08648548931853303</v>
+        <v>0.08629330853983948</v>
       </c>
       <c r="C56">
-        <v>43.49063873553204</v>
+        <v>42.81445565352436</v>
       </c>
       <c r="D56">
-        <v>71.50363873553204</v>
+        <v>71.63695565352437</v>
       </c>
       <c r="E56">
-        <v>40.263</v>
+        <v>41.07250000000001</v>
       </c>
       <c r="F56">
-        <v>43.713</v>
+        <v>44.52250000000001</v>
       </c>
       <c r="G56">
         <v>15.7</v>
@@ -5879,28 +5879,28 @@
         <v>11.5</v>
       </c>
       <c r="M56">
-        <v>2.4173289</v>
+        <v>2.462094250000001</v>
       </c>
       <c r="N56">
-        <v>9.082671099999999</v>
+        <v>9.03790575</v>
       </c>
       <c r="O56">
-        <v>2.452321197</v>
+        <v>2.4402345525</v>
       </c>
       <c r="P56">
-        <v>6.630349902999999</v>
+        <v>6.5976711975</v>
       </c>
       <c r="Q56">
-        <v>6.930349903</v>
+        <v>6.897671197500001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1406222376489848</v>
+        <v>0.1424230189774211</v>
       </c>
       <c r="T56">
-        <v>1.736702582735553</v>
+        <v>1.769684525174144</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.757317053546167</v>
+        <v>4.670820379845328</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08629330853983948</v>
+        <v>0.08610112776114592</v>
       </c>
       <c r="C57">
-        <v>42.81445565352436</v>
+        <v>42.13877063290047</v>
       </c>
       <c r="D57">
-        <v>71.63695565352437</v>
+        <v>71.77077063290048</v>
       </c>
       <c r="E57">
-        <v>41.07250000000001</v>
+        <v>41.88200000000001</v>
       </c>
       <c r="F57">
-        <v>44.52250000000001</v>
+        <v>45.33200000000001</v>
       </c>
       <c r="G57">
         <v>15.7</v>
@@ -5961,28 +5961,28 @@
         <v>11.5</v>
       </c>
       <c r="M57">
-        <v>2.462094250000001</v>
+        <v>2.506859600000001</v>
       </c>
       <c r="N57">
-        <v>9.03790575</v>
+        <v>8.9931404</v>
       </c>
       <c r="O57">
-        <v>2.4402345525</v>
+        <v>2.428147908</v>
       </c>
       <c r="P57">
-        <v>6.5976711975</v>
+        <v>6.564992492</v>
       </c>
       <c r="Q57">
-        <v>6.897671197500001</v>
+        <v>6.864992492000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1424230189774211</v>
+        <v>0.1443056540026044</v>
       </c>
       <c r="T57">
-        <v>1.769684525174144</v>
+        <v>1.804165646814487</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.670820379845328</v>
+        <v>4.587412873062375</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08610112776114592</v>
+        <v>0.08590894698245236</v>
       </c>
       <c r="C58">
-        <v>42.13877063290047</v>
+        <v>41.46358646996023</v>
       </c>
       <c r="D58">
-        <v>71.77077063290048</v>
+        <v>71.90508646996024</v>
       </c>
       <c r="E58">
-        <v>41.88200000000001</v>
+        <v>42.6915</v>
       </c>
       <c r="F58">
-        <v>45.33200000000001</v>
+        <v>46.14150000000001</v>
       </c>
       <c r="G58">
         <v>15.7</v>
@@ -6043,28 +6043,28 @@
         <v>11.5</v>
       </c>
       <c r="M58">
-        <v>2.506859600000001</v>
+        <v>2.55162495</v>
       </c>
       <c r="N58">
-        <v>8.9931404</v>
+        <v>8.948375049999999</v>
       </c>
       <c r="O58">
-        <v>2.428147908</v>
+        <v>2.4160612635</v>
       </c>
       <c r="P58">
-        <v>6.564992492</v>
+        <v>6.5323137865</v>
       </c>
       <c r="Q58">
-        <v>6.864992492000001</v>
+        <v>6.8323137865</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1443056540026044</v>
+        <v>0.1462758534475636</v>
       </c>
       <c r="T58">
-        <v>1.804165646814487</v>
+        <v>1.840250541554382</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.587412873062375</v>
+        <v>4.506931945464791</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08590894698245236</v>
+        <v>0.08677526620375881</v>
       </c>
       <c r="C59">
-        <v>41.46358646996023</v>
+        <v>40.05255438850666</v>
       </c>
       <c r="D59">
-        <v>71.90508646996024</v>
+        <v>71.30355438850667</v>
       </c>
       <c r="E59">
-        <v>42.6915</v>
+        <v>43.501</v>
       </c>
       <c r="F59">
-        <v>46.14150000000001</v>
+        <v>46.95100000000001</v>
       </c>
       <c r="G59">
         <v>15.7</v>
@@ -6125,45 +6125,45 @@
         <v>11.5</v>
       </c>
       <c r="M59">
-        <v>2.55162495</v>
+        <v>2.713767800000001</v>
       </c>
       <c r="N59">
-        <v>8.948375049999999</v>
+        <v>8.786232199999999</v>
       </c>
       <c r="O59">
-        <v>2.4160612635</v>
+        <v>2.372282694</v>
       </c>
       <c r="P59">
-        <v>6.5323137865</v>
+        <v>6.413949505999999</v>
       </c>
       <c r="Q59">
-        <v>6.8323137865</v>
+        <v>6.713949506</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1462758534475636</v>
+        <v>0.1483398719137115</v>
       </c>
       <c r="T59">
-        <v>1.840250541554382</v>
+        <v>1.878053764615225</v>
       </c>
       <c r="U59">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V59">
         <v>0.27</v>
       </c>
       <c r="W59">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>4.506931945464791</v>
+        <v>4.237650693622349</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08677526620375879</v>
+        <v>0.08660133542506523</v>
       </c>
       <c r="C60">
-        <v>40.05255438850667</v>
+        <v>39.36301506120555</v>
       </c>
       <c r="D60">
-        <v>71.30355438850667</v>
+        <v>71.42351506120555</v>
       </c>
       <c r="E60">
-        <v>43.501</v>
+        <v>44.3105</v>
       </c>
       <c r="F60">
-        <v>46.951</v>
+        <v>47.7605</v>
       </c>
       <c r="G60">
         <v>15.7</v>
@@ -6207,28 +6207,28 @@
         <v>11.5</v>
       </c>
       <c r="M60">
-        <v>2.7137678</v>
+        <v>2.7605569</v>
       </c>
       <c r="N60">
-        <v>8.786232200000001</v>
+        <v>8.739443099999999</v>
       </c>
       <c r="O60">
-        <v>2.372282694</v>
+        <v>2.359649637</v>
       </c>
       <c r="P60">
-        <v>6.413949506</v>
+        <v>6.379793462999999</v>
       </c>
       <c r="Q60">
-        <v>6.713949506000001</v>
+        <v>6.679793462999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1483398719137114</v>
+        <v>0.1505045742074762</v>
       </c>
       <c r="T60">
-        <v>1.878053764615224</v>
+        <v>1.917701047337571</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.23765069362235</v>
+        <v>4.165826105594853</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08660133542506523</v>
+        <v>0.08642740464637168</v>
       </c>
       <c r="C61">
-        <v>39.36301506120555</v>
+        <v>38.67388005636817</v>
       </c>
       <c r="D61">
-        <v>71.42351506120555</v>
+        <v>71.54388005636817</v>
       </c>
       <c r="E61">
-        <v>44.3105</v>
+        <v>45.12</v>
       </c>
       <c r="F61">
-        <v>47.7605</v>
+        <v>48.57</v>
       </c>
       <c r="G61">
         <v>15.7</v>
@@ -6289,28 +6289,28 @@
         <v>11.5</v>
       </c>
       <c r="M61">
-        <v>2.7605569</v>
+        <v>2.807346</v>
       </c>
       <c r="N61">
-        <v>8.739443099999999</v>
+        <v>8.692653999999999</v>
       </c>
       <c r="O61">
-        <v>2.359649637</v>
+        <v>2.34701658</v>
       </c>
       <c r="P61">
-        <v>6.379793462999999</v>
+        <v>6.345637419999999</v>
       </c>
       <c r="Q61">
-        <v>6.679793462999999</v>
+        <v>6.64563742</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1505045742074762</v>
+        <v>0.1527775116159292</v>
       </c>
       <c r="T61">
-        <v>1.917701047337571</v>
+        <v>1.959330694196034</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.165826105594853</v>
+        <v>4.096395670501605</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08642740464637168</v>
+        <v>0.08625347386767812</v>
       </c>
       <c r="C62">
-        <v>38.67388005636817</v>
+        <v>37.98515142157326</v>
       </c>
       <c r="D62">
-        <v>71.54388005636817</v>
+        <v>71.66465142157325</v>
       </c>
       <c r="E62">
-        <v>45.12</v>
+        <v>45.9295</v>
       </c>
       <c r="F62">
-        <v>48.57</v>
+        <v>49.3795</v>
       </c>
       <c r="G62">
         <v>15.7</v>
@@ -6371,28 +6371,28 @@
         <v>11.5</v>
       </c>
       <c r="M62">
-        <v>2.807346</v>
+        <v>2.8541351</v>
       </c>
       <c r="N62">
-        <v>8.692653999999999</v>
+        <v>8.645864899999999</v>
       </c>
       <c r="O62">
-        <v>2.34701658</v>
+        <v>2.334383523</v>
       </c>
       <c r="P62">
-        <v>6.345637419999999</v>
+        <v>6.311481377</v>
       </c>
       <c r="Q62">
-        <v>6.64563742</v>
+        <v>6.611481377</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1527775116159292</v>
+        <v>0.1551670099171234</v>
       </c>
       <c r="T62">
-        <v>1.959330694196034</v>
+        <v>2.003095194739548</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.096395670501605</v>
+        <v>4.029241643116332</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08625347386767812</v>
+        <v>0.08766364308898456</v>
       </c>
       <c r="C63">
-        <v>37.98515142157326</v>
+        <v>36.20806962585083</v>
       </c>
       <c r="D63">
-        <v>71.66465142157325</v>
+        <v>70.69706962585083</v>
       </c>
       <c r="E63">
-        <v>45.9295</v>
+        <v>46.739</v>
       </c>
       <c r="F63">
-        <v>49.3795</v>
+        <v>50.189</v>
       </c>
       <c r="G63">
         <v>15.7</v>
@@ -6453,45 +6453,45 @@
         <v>11.5</v>
       </c>
       <c r="M63">
-        <v>2.8541351</v>
+        <v>3.0765857</v>
       </c>
       <c r="N63">
-        <v>8.645864899999999</v>
+        <v>8.423414300000001</v>
       </c>
       <c r="O63">
-        <v>2.334383523</v>
+        <v>2.274321861</v>
       </c>
       <c r="P63">
-        <v>6.311481377</v>
+        <v>6.149092439</v>
       </c>
       <c r="Q63">
-        <v>6.611481377</v>
+        <v>6.449092439000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1551670099171234</v>
+        <v>0.1576822712868015</v>
       </c>
       <c r="T63">
-        <v>2.003095194739548</v>
+        <v>2.04916309004851</v>
       </c>
       <c r="U63">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V63">
         <v>0.27</v>
       </c>
       <c r="W63">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>4.029241643116332</v>
+        <v>3.737909852470549</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08766364308898456</v>
+        <v>0.08751526231029098</v>
       </c>
       <c r="C64">
-        <v>36.20806962585083</v>
+        <v>35.49914877220726</v>
       </c>
       <c r="D64">
-        <v>70.69706962585083</v>
+        <v>70.79764877220725</v>
       </c>
       <c r="E64">
-        <v>46.739</v>
+        <v>47.5485</v>
       </c>
       <c r="F64">
-        <v>50.189</v>
+        <v>50.9985</v>
       </c>
       <c r="G64">
         <v>15.7</v>
@@ -6535,28 +6535,28 @@
         <v>11.5</v>
       </c>
       <c r="M64">
-        <v>3.0765857</v>
+        <v>3.12620805</v>
       </c>
       <c r="N64">
-        <v>8.423414300000001</v>
+        <v>8.373791950000001</v>
       </c>
       <c r="O64">
-        <v>2.274321861</v>
+        <v>2.2609238265</v>
       </c>
       <c r="P64">
-        <v>6.149092439</v>
+        <v>6.1128681235</v>
       </c>
       <c r="Q64">
-        <v>6.449092439000001</v>
+        <v>6.412868123500001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1576822712868015</v>
+        <v>0.1603334927305162</v>
       </c>
       <c r="T64">
-        <v>2.04916309004851</v>
+        <v>2.097721141860658</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.737909852470549</v>
+        <v>3.678577950050382</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08751526231029098</v>
+        <v>0.08736688153159744</v>
       </c>
       <c r="C65">
-        <v>35.49914877220726</v>
+        <v>34.79051450971325</v>
       </c>
       <c r="D65">
-        <v>70.79764877220725</v>
+        <v>70.89851450971325</v>
       </c>
       <c r="E65">
-        <v>47.5485</v>
+        <v>48.358</v>
       </c>
       <c r="F65">
-        <v>50.9985</v>
+        <v>51.808</v>
       </c>
       <c r="G65">
         <v>15.7</v>
@@ -6617,28 +6617,28 @@
         <v>11.5</v>
       </c>
       <c r="M65">
-        <v>3.12620805</v>
+        <v>3.1758304</v>
       </c>
       <c r="N65">
-        <v>8.373791950000001</v>
+        <v>8.324169599999999</v>
       </c>
       <c r="O65">
-        <v>2.2609238265</v>
+        <v>2.247525792</v>
       </c>
       <c r="P65">
-        <v>6.1128681235</v>
+        <v>6.076643808</v>
       </c>
       <c r="Q65">
-        <v>6.412868123500001</v>
+        <v>6.376643808000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1603334927305162</v>
+        <v>0.1631320042544373</v>
       </c>
       <c r="T65">
-        <v>2.097721141860658</v>
+        <v>2.148976863217927</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.678577950050382</v>
+        <v>3.621100169580844</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08736688153159744</v>
+        <v>0.08721850075290387</v>
       </c>
       <c r="C66">
-        <v>34.79051450971325</v>
+        <v>34.0821680650397</v>
       </c>
       <c r="D66">
-        <v>70.89851450971325</v>
+        <v>70.9996680650397</v>
       </c>
       <c r="E66">
-        <v>48.358</v>
+        <v>49.1675</v>
       </c>
       <c r="F66">
-        <v>51.808</v>
+        <v>52.61750000000001</v>
       </c>
       <c r="G66">
         <v>15.7</v>
@@ -6699,28 +6699,28 @@
         <v>11.5</v>
       </c>
       <c r="M66">
-        <v>3.1758304</v>
+        <v>3.225452750000001</v>
       </c>
       <c r="N66">
-        <v>8.324169599999999</v>
+        <v>8.274547249999999</v>
       </c>
       <c r="O66">
-        <v>2.247525792</v>
+        <v>2.2341277575</v>
       </c>
       <c r="P66">
-        <v>6.076643808</v>
+        <v>6.0404194925</v>
       </c>
       <c r="Q66">
-        <v>6.376643808000001</v>
+        <v>6.340419492500001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1631320042544373</v>
+        <v>0.1660904307225825</v>
       </c>
       <c r="T66">
-        <v>2.148976863217927</v>
+        <v>2.203161482938467</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.621100169580844</v>
+        <v>3.565390936202677</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08721850075290387</v>
+        <v>0.0870701199742103</v>
       </c>
       <c r="C67">
-        <v>34.0821680650397</v>
+        <v>33.374110671868</v>
       </c>
       <c r="D67">
-        <v>70.9996680650397</v>
+        <v>71.101110671868</v>
       </c>
       <c r="E67">
-        <v>49.1675</v>
+        <v>49.977</v>
       </c>
       <c r="F67">
-        <v>52.61750000000001</v>
+        <v>53.42700000000001</v>
       </c>
       <c r="G67">
         <v>15.7</v>
@@ -6781,28 +6781,28 @@
         <v>11.5</v>
       </c>
       <c r="M67">
-        <v>3.225452750000001</v>
+        <v>3.2750751</v>
       </c>
       <c r="N67">
-        <v>8.274547249999999</v>
+        <v>8.2249249</v>
       </c>
       <c r="O67">
-        <v>2.2341277575</v>
+        <v>2.220729723</v>
       </c>
       <c r="P67">
-        <v>6.0404194925</v>
+        <v>6.004195177</v>
       </c>
       <c r="Q67">
-        <v>6.340419492500001</v>
+        <v>6.304195177</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1660904307225825</v>
+        <v>0.1692228822770891</v>
       </c>
       <c r="T67">
-        <v>2.203161482938467</v>
+        <v>2.260533433230803</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.565390936202677</v>
+        <v>3.511369861411727</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0870701199742103</v>
+        <v>0.08829121919551675</v>
       </c>
       <c r="C68">
-        <v>33.374110671868</v>
+        <v>31.73831194583335</v>
       </c>
       <c r="D68">
-        <v>71.101110671868</v>
+        <v>70.27481194583335</v>
       </c>
       <c r="E68">
-        <v>49.977</v>
+        <v>50.7865</v>
       </c>
       <c r="F68">
-        <v>53.42700000000001</v>
+        <v>54.23650000000001</v>
       </c>
       <c r="G68">
         <v>15.7</v>
@@ -6863,45 +6863,45 @@
         <v>11.5</v>
       </c>
       <c r="M68">
-        <v>3.2750751</v>
+        <v>3.47655965</v>
       </c>
       <c r="N68">
-        <v>8.2249249</v>
+        <v>8.02344035</v>
       </c>
       <c r="O68">
-        <v>2.220729723</v>
+        <v>2.1663288945</v>
       </c>
       <c r="P68">
-        <v>6.004195177</v>
+        <v>5.8571114555</v>
       </c>
       <c r="Q68">
-        <v>6.304195177</v>
+        <v>6.157111455500001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1692228822770891</v>
+        <v>0.1725451793803538</v>
       </c>
       <c r="T68">
-        <v>2.260533433230803</v>
+        <v>2.321382471419646</v>
       </c>
       <c r="U68">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V68">
         <v>0.27</v>
       </c>
       <c r="W68">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.511369861411727</v>
+        <v>3.307867880247646</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08829121919551675</v>
+        <v>0.0881632784168232</v>
       </c>
       <c r="C69">
-        <v>31.73831194583335</v>
+        <v>31.01448565349888</v>
       </c>
       <c r="D69">
-        <v>70.27481194583335</v>
+        <v>70.36048565349888</v>
       </c>
       <c r="E69">
-        <v>50.7865</v>
+        <v>51.596</v>
       </c>
       <c r="F69">
-        <v>54.23650000000001</v>
+        <v>55.04600000000001</v>
       </c>
       <c r="G69">
         <v>15.7</v>
@@ -6945,28 +6945,28 @@
         <v>11.5</v>
       </c>
       <c r="M69">
-        <v>3.47655965</v>
+        <v>3.528448600000001</v>
       </c>
       <c r="N69">
-        <v>8.02344035</v>
+        <v>7.971551399999999</v>
       </c>
       <c r="O69">
-        <v>2.1663288945</v>
+        <v>2.152318878</v>
       </c>
       <c r="P69">
-        <v>5.8571114555</v>
+        <v>5.819232521999999</v>
       </c>
       <c r="Q69">
-        <v>6.157111455500001</v>
+        <v>6.119232522</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1725451793803538</v>
+        <v>0.1760751200525725</v>
       </c>
       <c r="T69">
-        <v>2.321382471419646</v>
+        <v>2.386034574495291</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.307867880247646</v>
+        <v>3.259222764361651</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0881632784168232</v>
+        <v>0.08803533763812962</v>
       </c>
       <c r="C70">
-        <v>31.01448565349888</v>
+        <v>30.29086850988371</v>
       </c>
       <c r="D70">
-        <v>70.36048565349888</v>
+        <v>70.44636850988371</v>
       </c>
       <c r="E70">
-        <v>51.596</v>
+        <v>52.4055</v>
       </c>
       <c r="F70">
-        <v>55.04600000000001</v>
+        <v>55.85550000000001</v>
       </c>
       <c r="G70">
         <v>15.7</v>
@@ -7027,28 +7027,28 @@
         <v>11.5</v>
       </c>
       <c r="M70">
-        <v>3.528448600000001</v>
+        <v>3.580337550000001</v>
       </c>
       <c r="N70">
-        <v>7.971551399999999</v>
+        <v>7.919662449999999</v>
       </c>
       <c r="O70">
-        <v>2.152318878</v>
+        <v>2.1383088615</v>
       </c>
       <c r="P70">
-        <v>5.819232521999999</v>
+        <v>5.781353588499999</v>
       </c>
       <c r="Q70">
-        <v>6.119232522</v>
+        <v>6.0813535885</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1760751200525725</v>
+        <v>0.1798327988326762</v>
       </c>
       <c r="T70">
-        <v>2.386034574495291</v>
+        <v>2.454857780995171</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.259222764361651</v>
+        <v>3.21198765183467</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08803533763812962</v>
+        <v>0.08790739685943608</v>
       </c>
       <c r="C71">
-        <v>30.29086850988371</v>
+        <v>29.56746128179213</v>
       </c>
       <c r="D71">
-        <v>70.44636850988371</v>
+        <v>70.53246128179214</v>
       </c>
       <c r="E71">
-        <v>52.4055</v>
+        <v>53.215</v>
       </c>
       <c r="F71">
-        <v>55.85550000000001</v>
+        <v>56.66500000000001</v>
       </c>
       <c r="G71">
         <v>15.7</v>
@@ -7109,28 +7109,28 @@
         <v>11.5</v>
       </c>
       <c r="M71">
-        <v>3.580337550000001</v>
+        <v>3.632226500000001</v>
       </c>
       <c r="N71">
-        <v>7.919662449999999</v>
+        <v>7.867773499999999</v>
       </c>
       <c r="O71">
-        <v>2.1383088615</v>
+        <v>2.124298845</v>
       </c>
       <c r="P71">
-        <v>5.781353588499999</v>
+        <v>5.743474655</v>
       </c>
       <c r="Q71">
-        <v>6.0813535885</v>
+        <v>6.043474655000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1798327988326762</v>
+        <v>0.1838409895314536</v>
       </c>
       <c r="T71">
-        <v>2.454857780995171</v>
+        <v>2.52826920126171</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.21198765183467</v>
+        <v>3.166102113951318</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08790739685943608</v>
+        <v>0.08777945608074253</v>
       </c>
       <c r="C72">
-        <v>29.56746128179213</v>
+        <v>28.84426473978148</v>
       </c>
       <c r="D72">
-        <v>70.53246128179214</v>
+        <v>70.61876473978148</v>
       </c>
       <c r="E72">
-        <v>53.215</v>
+        <v>54.0245</v>
       </c>
       <c r="F72">
-        <v>56.66500000000001</v>
+        <v>57.47450000000001</v>
       </c>
       <c r="G72">
         <v>15.7</v>
@@ -7191,28 +7191,28 @@
         <v>11.5</v>
       </c>
       <c r="M72">
-        <v>3.632226500000001</v>
+        <v>3.684115450000001</v>
       </c>
       <c r="N72">
-        <v>7.867773499999999</v>
+        <v>7.81588455</v>
       </c>
       <c r="O72">
-        <v>2.124298845</v>
+        <v>2.1102888285</v>
       </c>
       <c r="P72">
-        <v>5.743474655</v>
+        <v>5.7055957215</v>
       </c>
       <c r="Q72">
-        <v>6.043474655000001</v>
+        <v>6.005595721500001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1838409895314536</v>
+        <v>0.1881256071749742</v>
       </c>
       <c r="T72">
-        <v>2.52826920126171</v>
+        <v>2.606743478098354</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.166102113951318</v>
+        <v>3.121509126430877</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08777945608074252</v>
+        <v>0.08765151530204895</v>
       </c>
       <c r="C73">
-        <v>28.8442647397815</v>
+        <v>28.12127965818521</v>
       </c>
       <c r="D73">
-        <v>70.6187647397815</v>
+        <v>70.7052796581852</v>
       </c>
       <c r="E73">
-        <v>54.0245</v>
+        <v>54.834</v>
       </c>
       <c r="F73">
-        <v>57.4745</v>
+        <v>58.284</v>
       </c>
       <c r="G73">
         <v>15.7</v>
@@ -7273,28 +7273,28 @@
         <v>11.5</v>
       </c>
       <c r="M73">
-        <v>3.68411545</v>
+        <v>3.7360044</v>
       </c>
       <c r="N73">
-        <v>7.81588455</v>
+        <v>7.763995599999999</v>
       </c>
       <c r="O73">
-        <v>2.1102888285</v>
+        <v>2.096278812</v>
       </c>
       <c r="P73">
-        <v>5.7055957215</v>
+        <v>5.667716788</v>
       </c>
       <c r="Q73">
-        <v>6.005595721500001</v>
+        <v>5.967716788000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1881256071749742</v>
+        <v>0.1927162689358891</v>
       </c>
       <c r="T73">
-        <v>2.606743478098354</v>
+        <v>2.69082306042333</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.121509126430877</v>
+        <v>3.078154833008226</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08765151530204895</v>
+        <v>0.08752357452335539</v>
       </c>
       <c r="C74">
-        <v>28.12127965818521</v>
+        <v>27.39850681513582</v>
       </c>
       <c r="D74">
-        <v>70.7052796581852</v>
+        <v>70.79200681513582</v>
       </c>
       <c r="E74">
-        <v>54.834</v>
+        <v>55.6435</v>
       </c>
       <c r="F74">
-        <v>58.284</v>
+        <v>59.0935</v>
       </c>
       <c r="G74">
         <v>15.7</v>
@@ -7355,28 +7355,28 @@
         <v>11.5</v>
       </c>
       <c r="M74">
-        <v>3.7360044</v>
+        <v>3.78789335</v>
       </c>
       <c r="N74">
-        <v>7.763995599999999</v>
+        <v>7.71210665</v>
       </c>
       <c r="O74">
-        <v>2.096278812</v>
+        <v>2.0822687955</v>
       </c>
       <c r="P74">
-        <v>5.667716788</v>
+        <v>5.6298378545</v>
       </c>
       <c r="Q74">
-        <v>5.967716788000001</v>
+        <v>5.929837854500001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1927162689358891</v>
+        <v>0.1976469797161311</v>
       </c>
       <c r="T74">
-        <v>2.69082306042333</v>
+        <v>2.781130759957564</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.078154833008226</v>
+        <v>3.03598832844647</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08752357452335539</v>
+        <v>0.09160919374466184</v>
       </c>
       <c r="C75">
-        <v>27.39850681513582</v>
+        <v>23.92061352290381</v>
       </c>
       <c r="D75">
-        <v>70.79200681513582</v>
+        <v>68.12361352290381</v>
       </c>
       <c r="E75">
-        <v>55.6435</v>
+        <v>56.453</v>
       </c>
       <c r="F75">
-        <v>59.0935</v>
+        <v>59.903</v>
       </c>
       <c r="G75">
         <v>15.7</v>
@@ -7437,45 +7437,45 @@
         <v>11.5</v>
       </c>
       <c r="M75">
-        <v>3.78789335</v>
+        <v>4.307025700000001</v>
       </c>
       <c r="N75">
-        <v>7.71210665</v>
+        <v>7.192974299999999</v>
       </c>
       <c r="O75">
-        <v>2.0822687955</v>
+        <v>1.942103061</v>
       </c>
       <c r="P75">
-        <v>5.6298378545</v>
+        <v>5.250871238999999</v>
       </c>
       <c r="Q75">
-        <v>5.929837854500001</v>
+        <v>5.550871239</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1976469797161311</v>
+        <v>0.202956975941007</v>
       </c>
       <c r="T75">
-        <v>2.781130759957564</v>
+        <v>2.878385205609816</v>
       </c>
       <c r="U75">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V75">
         <v>0.27</v>
       </c>
       <c r="W75">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y75">
-        <v>3.03598832844647</v>
+        <v>2.670056043547639</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09160919374466184</v>
+        <v>0.09153819296596827</v>
       </c>
       <c r="C76">
-        <v>23.92061352290381</v>
+        <v>23.15576677479379</v>
       </c>
       <c r="D76">
-        <v>68.12361352290381</v>
+        <v>68.16826677479379</v>
       </c>
       <c r="E76">
-        <v>56.453</v>
+        <v>57.2625</v>
       </c>
       <c r="F76">
-        <v>59.903</v>
+        <v>60.71250000000001</v>
       </c>
       <c r="G76">
         <v>15.7</v>
@@ -7519,28 +7519,28 @@
         <v>11.5</v>
       </c>
       <c r="M76">
-        <v>4.307025700000001</v>
+        <v>4.365228750000001</v>
       </c>
       <c r="N76">
-        <v>7.192974299999999</v>
+        <v>7.134771249999999</v>
       </c>
       <c r="O76">
-        <v>1.942103061</v>
+        <v>1.9263882375</v>
       </c>
       <c r="P76">
-        <v>5.250871238999999</v>
+        <v>5.208383012499999</v>
       </c>
       <c r="Q76">
-        <v>5.550871239</v>
+        <v>5.5083830125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.202956975941007</v>
+        <v>0.2086917718638731</v>
       </c>
       <c r="T76">
-        <v>2.878385205609816</v>
+        <v>2.983420006914248</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.670056043547639</v>
+        <v>2.634455296300336</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09153819296596827</v>
+        <v>0.09146719218727473</v>
       </c>
       <c r="C77">
-        <v>23.15576677479379</v>
+        <v>22.39097860316306</v>
       </c>
       <c r="D77">
-        <v>68.16826677479379</v>
+        <v>68.21297860316307</v>
       </c>
       <c r="E77">
-        <v>57.2625</v>
+        <v>58.072</v>
       </c>
       <c r="F77">
-        <v>60.71250000000001</v>
+        <v>61.52200000000001</v>
       </c>
       <c r="G77">
         <v>15.7</v>
@@ -7601,28 +7601,28 @@
         <v>11.5</v>
       </c>
       <c r="M77">
-        <v>4.365228750000001</v>
+        <v>4.4234318</v>
       </c>
       <c r="N77">
-        <v>7.134771249999999</v>
+        <v>7.0765682</v>
       </c>
       <c r="O77">
-        <v>1.9263882375</v>
+        <v>1.910673414</v>
       </c>
       <c r="P77">
-        <v>5.208383012499999</v>
+        <v>5.165894785999999</v>
       </c>
       <c r="Q77">
-        <v>5.5083830125</v>
+        <v>5.465894786</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2086917718638731</v>
+        <v>0.214904467446978</v>
       </c>
       <c r="T77">
-        <v>2.983420006914248</v>
+        <v>3.097207708327384</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.634455296300336</v>
+        <v>2.599791410822701</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09146719218727473</v>
+        <v>0.09139619140858116</v>
       </c>
       <c r="C78">
-        <v>22.39097860316306</v>
+        <v>21.62624912334896</v>
       </c>
       <c r="D78">
-        <v>68.21297860316307</v>
+        <v>68.25774912334896</v>
       </c>
       <c r="E78">
-        <v>58.072</v>
+        <v>58.8815</v>
       </c>
       <c r="F78">
-        <v>61.52200000000001</v>
+        <v>62.33150000000001</v>
       </c>
       <c r="G78">
         <v>15.7</v>
@@ -7683,28 +7683,28 @@
         <v>11.5</v>
       </c>
       <c r="M78">
-        <v>4.4234318</v>
+        <v>4.481634850000001</v>
       </c>
       <c r="N78">
-        <v>7.0765682</v>
+        <v>7.018365149999999</v>
       </c>
       <c r="O78">
-        <v>1.910673414</v>
+        <v>1.8949585905</v>
       </c>
       <c r="P78">
-        <v>5.165894785999999</v>
+        <v>5.123406559499999</v>
       </c>
       <c r="Q78">
-        <v>5.465894786</v>
+        <v>5.4234065595</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.214904467446978</v>
+        <v>0.2216573974286137</v>
       </c>
       <c r="T78">
-        <v>3.097207708327384</v>
+        <v>3.220889992472095</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.599791410822701</v>
+        <v>2.566027886006821</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09139619140858116</v>
+        <v>0.09132519062988759</v>
       </c>
       <c r="C79">
-        <v>21.62624912334896</v>
+        <v>20.8615784509917</v>
       </c>
       <c r="D79">
-        <v>68.25774912334896</v>
+        <v>68.3025784509917</v>
       </c>
       <c r="E79">
-        <v>58.8815</v>
+        <v>59.691</v>
       </c>
       <c r="F79">
-        <v>62.33150000000001</v>
+        <v>63.14100000000001</v>
       </c>
       <c r="G79">
         <v>15.7</v>
@@ -7765,28 +7765,28 @@
         <v>11.5</v>
       </c>
       <c r="M79">
-        <v>4.481634850000001</v>
+        <v>4.539837900000001</v>
       </c>
       <c r="N79">
-        <v>7.018365149999999</v>
+        <v>6.960162099999999</v>
       </c>
       <c r="O79">
-        <v>1.8949585905</v>
+        <v>1.879243767</v>
       </c>
       <c r="P79">
-        <v>5.123406559499999</v>
+        <v>5.080918333</v>
       </c>
       <c r="Q79">
-        <v>5.4234065595</v>
+        <v>5.380918333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2216573974286137</v>
+        <v>0.2290242301358527</v>
       </c>
       <c r="T79">
-        <v>3.220889992472095</v>
+        <v>3.355816120629963</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.566027886006821</v>
+        <v>2.533130092596477</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09132519062988759</v>
+        <v>0.09125418985119403</v>
       </c>
       <c r="C80">
-        <v>20.8615784509917</v>
+        <v>20.09696670203554</v>
       </c>
       <c r="D80">
-        <v>68.3025784509917</v>
+        <v>68.34746670203555</v>
       </c>
       <c r="E80">
-        <v>59.691</v>
+        <v>60.5005</v>
       </c>
       <c r="F80">
-        <v>63.14100000000001</v>
+        <v>63.95050000000001</v>
       </c>
       <c r="G80">
         <v>15.7</v>
@@ -7847,28 +7847,28 @@
         <v>11.5</v>
       </c>
       <c r="M80">
-        <v>4.539837900000001</v>
+        <v>4.598040950000001</v>
       </c>
       <c r="N80">
-        <v>6.960162099999999</v>
+        <v>6.901959049999999</v>
       </c>
       <c r="O80">
-        <v>1.879243767</v>
+        <v>1.8635289435</v>
       </c>
       <c r="P80">
-        <v>5.080918333</v>
+        <v>5.0384301065</v>
       </c>
       <c r="Q80">
-        <v>5.380918333</v>
+        <v>5.338430106500001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2290242301358527</v>
+        <v>0.2370926659580668</v>
       </c>
       <c r="T80">
-        <v>3.355816120629963</v>
+        <v>3.503592356231437</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.533130092596477</v>
+        <v>2.501065154715509</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09125418985119403</v>
+        <v>0.09346078907250047</v>
       </c>
       <c r="C81">
-        <v>20.09696670203554</v>
+        <v>17.91943113303499</v>
       </c>
       <c r="D81">
-        <v>68.34746670203555</v>
+        <v>66.97943113303499</v>
       </c>
       <c r="E81">
-        <v>60.5005</v>
+        <v>61.31</v>
       </c>
       <c r="F81">
-        <v>63.95050000000001</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="G81">
         <v>15.7</v>
@@ -7929,45 +7929,45 @@
         <v>11.5</v>
       </c>
       <c r="M81">
-        <v>4.598040950000001</v>
+        <v>4.908808000000001</v>
       </c>
       <c r="N81">
-        <v>6.901959049999999</v>
+        <v>6.591191999999999</v>
       </c>
       <c r="O81">
-        <v>1.8635289435</v>
+        <v>1.77962184</v>
       </c>
       <c r="P81">
-        <v>5.0384301065</v>
+        <v>4.81157016</v>
       </c>
       <c r="Q81">
-        <v>5.338430106500001</v>
+        <v>5.11157016</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2370926659580668</v>
+        <v>0.2459679453625024</v>
       </c>
       <c r="T81">
-        <v>3.503592356231437</v>
+        <v>3.666146215393058</v>
       </c>
       <c r="U81">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V81">
         <v>0.27</v>
       </c>
       <c r="W81">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y81">
-        <v>2.501065154715509</v>
+        <v>2.342727603116683</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09346078907250047</v>
+        <v>0.0934182582938069</v>
       </c>
       <c r="C82">
-        <v>17.91943113303499</v>
+        <v>17.1357813311454</v>
       </c>
       <c r="D82">
-        <v>66.97943113303499</v>
+        <v>67.0052813311454</v>
       </c>
       <c r="E82">
-        <v>61.31</v>
+        <v>62.1195</v>
       </c>
       <c r="F82">
-        <v>64.76000000000001</v>
+        <v>65.56950000000001</v>
       </c>
       <c r="G82">
         <v>15.7</v>
@@ -8011,28 +8011,28 @@
         <v>11.5</v>
       </c>
       <c r="M82">
-        <v>4.908808000000001</v>
+        <v>4.9701681</v>
       </c>
       <c r="N82">
-        <v>6.591191999999999</v>
+        <v>6.5298319</v>
       </c>
       <c r="O82">
-        <v>1.77962184</v>
+        <v>1.763054613</v>
       </c>
       <c r="P82">
-        <v>4.81157016</v>
+        <v>4.766777287</v>
       </c>
       <c r="Q82">
-        <v>5.11157016</v>
+        <v>5.066777287000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2459679453625024</v>
+        <v>0.2557774647042469</v>
       </c>
       <c r="T82">
-        <v>3.666146215393058</v>
+        <v>3.845811007098008</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.342727603116683</v>
+        <v>2.313805040115243</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.0934182582938069</v>
+        <v>0.09337572751511335</v>
       </c>
       <c r="C83">
-        <v>17.1357813311454</v>
+        <v>16.35215149033129</v>
       </c>
       <c r="D83">
-        <v>67.0052813311454</v>
+        <v>67.0311514903313</v>
       </c>
       <c r="E83">
-        <v>62.1195</v>
+        <v>62.929</v>
       </c>
       <c r="F83">
-        <v>65.56950000000001</v>
+        <v>66.379</v>
       </c>
       <c r="G83">
         <v>15.7</v>
@@ -8093,28 +8093,28 @@
         <v>11.5</v>
       </c>
       <c r="M83">
-        <v>4.9701681</v>
+        <v>5.031528200000001</v>
       </c>
       <c r="N83">
-        <v>6.5298319</v>
+        <v>6.468471799999999</v>
       </c>
       <c r="O83">
-        <v>1.763054613</v>
+        <v>1.746487386</v>
       </c>
       <c r="P83">
-        <v>4.766777287</v>
+        <v>4.721984413999999</v>
       </c>
       <c r="Q83">
-        <v>5.066777287000001</v>
+        <v>5.021984413999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2557774647042469</v>
+        <v>0.2666769306395186</v>
       </c>
       <c r="T83">
-        <v>3.845811007098008</v>
+        <v>4.045438553436842</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.313805040115243</v>
+        <v>2.28558790547969</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09337572751511335</v>
+        <v>0.09333319673641979</v>
       </c>
       <c r="C84">
-        <v>16.35215149033129</v>
+        <v>15.56854163372205</v>
       </c>
       <c r="D84">
-        <v>67.0311514903313</v>
+        <v>67.05704163372205</v>
       </c>
       <c r="E84">
-        <v>62.929</v>
+        <v>63.7385</v>
       </c>
       <c r="F84">
-        <v>66.379</v>
+        <v>67.1885</v>
       </c>
       <c r="G84">
         <v>15.7</v>
@@ -8175,28 +8175,28 @@
         <v>11.5</v>
       </c>
       <c r="M84">
-        <v>5.031528200000001</v>
+        <v>5.092888300000001</v>
       </c>
       <c r="N84">
-        <v>6.468471799999999</v>
+        <v>6.407111699999999</v>
       </c>
       <c r="O84">
-        <v>1.746487386</v>
+        <v>1.729920159</v>
       </c>
       <c r="P84">
-        <v>4.721984413999999</v>
+        <v>4.677191540999999</v>
       </c>
       <c r="Q84">
-        <v>5.021984413999999</v>
+        <v>4.977191541</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2666769306395186</v>
+        <v>0.2788586866848224</v>
       </c>
       <c r="T84">
-        <v>4.045438553436842</v>
+        <v>4.268551693462597</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.28558790547969</v>
+        <v>2.258050701799212</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09333319673641979</v>
+        <v>0.09329066595772623</v>
       </c>
       <c r="C85">
-        <v>15.56854163372205</v>
+        <v>14.78495178448269</v>
       </c>
       <c r="D85">
-        <v>67.05704163372205</v>
+        <v>67.08295178448269</v>
       </c>
       <c r="E85">
-        <v>63.7385</v>
+        <v>64.548</v>
       </c>
       <c r="F85">
-        <v>67.1885</v>
+        <v>67.998</v>
       </c>
       <c r="G85">
         <v>15.7</v>
@@ -8257,28 +8257,28 @@
         <v>11.5</v>
       </c>
       <c r="M85">
-        <v>5.092888300000001</v>
+        <v>5.154248400000001</v>
       </c>
       <c r="N85">
-        <v>6.407111699999999</v>
+        <v>6.345751599999999</v>
       </c>
       <c r="O85">
-        <v>1.729920159</v>
+        <v>1.713352932</v>
       </c>
       <c r="P85">
-        <v>4.677191540999999</v>
+        <v>4.632398667999999</v>
       </c>
       <c r="Q85">
-        <v>4.977191541</v>
+        <v>4.932398667999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2788586866848224</v>
+        <v>0.292563162235789</v>
       </c>
       <c r="T85">
-        <v>4.268551693462597</v>
+        <v>4.519553975991572</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.258050701799212</v>
+        <v>2.231169145825412</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09329066595772623</v>
+        <v>0.09324813517903266</v>
       </c>
       <c r="C86">
-        <v>14.78495178448269</v>
+        <v>14.00138196581415</v>
       </c>
       <c r="D86">
-        <v>67.08295178448269</v>
+        <v>67.10888196581415</v>
       </c>
       <c r="E86">
-        <v>64.548</v>
+        <v>65.3575</v>
       </c>
       <c r="F86">
-        <v>67.998</v>
+        <v>68.8075</v>
       </c>
       <c r="G86">
         <v>15.7</v>
@@ -8339,28 +8339,28 @@
         <v>11.5</v>
       </c>
       <c r="M86">
-        <v>5.154248400000001</v>
+        <v>5.215608500000001</v>
       </c>
       <c r="N86">
-        <v>6.345751599999999</v>
+        <v>6.284391499999999</v>
       </c>
       <c r="O86">
-        <v>1.713352932</v>
+        <v>1.696785705</v>
       </c>
       <c r="P86">
-        <v>4.632398667999999</v>
+        <v>4.587605794999999</v>
       </c>
       <c r="Q86">
-        <v>4.932398667999999</v>
+        <v>4.887605795</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2925631622357889</v>
+        <v>0.3080949011935511</v>
       </c>
       <c r="T86">
-        <v>4.519553975991569</v>
+        <v>4.804023229524406</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.231169145825412</v>
+        <v>2.204920097050996</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09324813517903266</v>
+        <v>0.09320560440033912</v>
       </c>
       <c r="C87">
-        <v>14.00138196581415</v>
+        <v>13.21783220095317</v>
       </c>
       <c r="D87">
-        <v>67.10888196581415</v>
+        <v>67.13483220095317</v>
       </c>
       <c r="E87">
-        <v>65.3575</v>
+        <v>66.167</v>
       </c>
       <c r="F87">
-        <v>68.8075</v>
+        <v>69.617</v>
       </c>
       <c r="G87">
         <v>15.7</v>
@@ -8421,28 +8421,28 @@
         <v>11.5</v>
       </c>
       <c r="M87">
-        <v>5.215608500000001</v>
+        <v>5.276968600000001</v>
       </c>
       <c r="N87">
-        <v>6.284391499999999</v>
+        <v>6.223031399999999</v>
       </c>
       <c r="O87">
-        <v>1.696785705</v>
+        <v>1.680218478</v>
       </c>
       <c r="P87">
-        <v>4.587605794999999</v>
+        <v>4.542812922</v>
       </c>
       <c r="Q87">
-        <v>4.887605795</v>
+        <v>4.842812922</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3080949011935511</v>
+        <v>0.3258454600024222</v>
       </c>
       <c r="T87">
-        <v>4.804023229524406</v>
+        <v>5.129130947847649</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.204920097050996</v>
+        <v>2.179281491271333</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09320560440033912</v>
+        <v>0.09316307362164555</v>
       </c>
       <c r="C88">
-        <v>13.21783220095317</v>
+        <v>12.43430251317251</v>
       </c>
       <c r="D88">
-        <v>67.13483220095317</v>
+        <v>67.16080251317251</v>
       </c>
       <c r="E88">
-        <v>66.167</v>
+        <v>66.9765</v>
       </c>
       <c r="F88">
-        <v>69.617</v>
+        <v>70.4265</v>
       </c>
       <c r="G88">
         <v>15.7</v>
@@ -8503,28 +8503,28 @@
         <v>11.5</v>
       </c>
       <c r="M88">
-        <v>5.276968600000001</v>
+        <v>5.338328700000001</v>
       </c>
       <c r="N88">
-        <v>6.223031399999999</v>
+        <v>6.161671299999999</v>
       </c>
       <c r="O88">
-        <v>1.680218478</v>
+        <v>1.663651251</v>
       </c>
       <c r="P88">
-        <v>4.542812922</v>
+        <v>4.498020048999999</v>
       </c>
       <c r="Q88">
-        <v>4.842812922</v>
+        <v>4.798020049</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3258454600024222</v>
+        <v>0.346326874012658</v>
       </c>
       <c r="T88">
-        <v>5.129130947847649</v>
+        <v>5.504255238220621</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.179281491271333</v>
+        <v>2.154232278727984</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09316307362164555</v>
+        <v>0.09312054284295199</v>
       </c>
       <c r="C89">
-        <v>12.43430251317251</v>
+        <v>11.65079292578091</v>
       </c>
       <c r="D89">
-        <v>67.16080251317251</v>
+        <v>67.18679292578091</v>
       </c>
       <c r="E89">
-        <v>66.9765</v>
+        <v>67.786</v>
       </c>
       <c r="F89">
-        <v>70.4265</v>
+        <v>71.236</v>
       </c>
       <c r="G89">
         <v>15.7</v>
@@ -8585,28 +8585,28 @@
         <v>11.5</v>
       </c>
       <c r="M89">
-        <v>5.338328700000001</v>
+        <v>5.399688800000001</v>
       </c>
       <c r="N89">
-        <v>6.161671299999999</v>
+        <v>6.100311199999999</v>
       </c>
       <c r="O89">
-        <v>1.663651251</v>
+        <v>1.647084024</v>
       </c>
       <c r="P89">
-        <v>4.498020048999999</v>
+        <v>4.453227176</v>
       </c>
       <c r="Q89">
-        <v>4.798020049</v>
+        <v>4.753227176</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.346326874012658</v>
+        <v>0.3702218570245999</v>
       </c>
       <c r="T89">
-        <v>5.504255238220621</v>
+        <v>5.941900243655756</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.154232278727984</v>
+        <v>2.129752366469712</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09312054284295199</v>
+        <v>0.09307801206425842</v>
       </c>
       <c r="C90">
-        <v>11.65079292578091</v>
+        <v>10.86730346212322</v>
       </c>
       <c r="D90">
-        <v>67.18679292578091</v>
+        <v>67.21280346212322</v>
       </c>
       <c r="E90">
-        <v>67.786</v>
+        <v>68.5955</v>
       </c>
       <c r="F90">
-        <v>71.236</v>
+        <v>72.0455</v>
       </c>
       <c r="G90">
         <v>15.7</v>
@@ -8667,28 +8667,28 @@
         <v>11.5</v>
       </c>
       <c r="M90">
-        <v>5.399688800000001</v>
+        <v>5.461048900000001</v>
       </c>
       <c r="N90">
-        <v>6.100311199999999</v>
+        <v>6.038951099999999</v>
       </c>
       <c r="O90">
-        <v>1.647084024</v>
+        <v>1.630516797</v>
       </c>
       <c r="P90">
-        <v>4.453227176</v>
+        <v>4.408434303</v>
       </c>
       <c r="Q90">
-        <v>4.753227176</v>
+        <v>4.708434303000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3702218570245999</v>
+        <v>0.3984613824023494</v>
       </c>
       <c r="T90">
-        <v>5.941900243655756</v>
+        <v>6.459117068260914</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.129752366469712</v>
+        <v>2.105822564599266</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09307801206425842</v>
+        <v>0.09303548128556487</v>
       </c>
       <c r="C91">
-        <v>10.86730346212322</v>
+        <v>10.08383414558045</v>
       </c>
       <c r="D91">
-        <v>67.21280346212322</v>
+        <v>67.23883414558046</v>
       </c>
       <c r="E91">
-        <v>68.5955</v>
+        <v>69.405</v>
       </c>
       <c r="F91">
-        <v>72.0455</v>
+        <v>72.855</v>
       </c>
       <c r="G91">
         <v>15.7</v>
@@ -8749,28 +8749,28 @@
         <v>11.5</v>
       </c>
       <c r="M91">
-        <v>5.461048900000001</v>
+        <v>5.522409000000001</v>
       </c>
       <c r="N91">
-        <v>6.038951099999999</v>
+        <v>5.977590999999999</v>
       </c>
       <c r="O91">
-        <v>1.630516797</v>
+        <v>1.61394957</v>
       </c>
       <c r="P91">
-        <v>4.408434303</v>
+        <v>4.363641429999999</v>
       </c>
       <c r="Q91">
-        <v>4.708434303000001</v>
+        <v>4.66364143</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3984613824023494</v>
+        <v>0.4323488128556487</v>
       </c>
       <c r="T91">
-        <v>6.459117068260914</v>
+        <v>7.079777257787105</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.105822564599266</v>
+        <v>2.082424536103718</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09303548128556487</v>
+        <v>0.09299295050687131</v>
       </c>
       <c r="C92">
-        <v>10.08383414558045</v>
+        <v>9.300384999569872</v>
       </c>
       <c r="D92">
-        <v>67.23883414558046</v>
+        <v>67.26488499956987</v>
       </c>
       <c r="E92">
-        <v>69.405</v>
+        <v>70.2145</v>
       </c>
       <c r="F92">
-        <v>72.855</v>
+        <v>73.6645</v>
       </c>
       <c r="G92">
         <v>15.7</v>
@@ -8831,28 +8831,28 @@
         <v>11.5</v>
       </c>
       <c r="M92">
-        <v>5.522409000000001</v>
+        <v>5.5837691</v>
       </c>
       <c r="N92">
-        <v>5.977590999999999</v>
+        <v>5.9162309</v>
       </c>
       <c r="O92">
-        <v>1.61394957</v>
+        <v>1.597382343</v>
       </c>
       <c r="P92">
-        <v>4.363641429999999</v>
+        <v>4.318848556999999</v>
       </c>
       <c r="Q92">
-        <v>4.66364143</v>
+        <v>4.618848557</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4323488128556487</v>
+        <v>0.4737667834096813</v>
       </c>
       <c r="T92">
-        <v>7.079777257787105</v>
+        <v>7.838361933874673</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.082424536103718</v>
+        <v>2.059540749992689</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09299295050687131</v>
+        <v>0.09295041972817775</v>
       </c>
       <c r="C93">
-        <v>9.300384999569872</v>
+        <v>8.516956047545037</v>
       </c>
       <c r="D93">
-        <v>67.26488499956987</v>
+        <v>67.29095604754504</v>
       </c>
       <c r="E93">
-        <v>70.2145</v>
+        <v>71.024</v>
       </c>
       <c r="F93">
-        <v>73.6645</v>
+        <v>74.474</v>
       </c>
       <c r="G93">
         <v>15.7</v>
@@ -8913,28 +8913,28 @@
         <v>11.5</v>
       </c>
       <c r="M93">
-        <v>5.5837691</v>
+        <v>5.6451292</v>
       </c>
       <c r="N93">
-        <v>5.9162309</v>
+        <v>5.8548708</v>
       </c>
       <c r="O93">
-        <v>1.597382343</v>
+        <v>1.580815116</v>
       </c>
       <c r="P93">
-        <v>4.318848556999999</v>
+        <v>4.274055683999999</v>
       </c>
       <c r="Q93">
-        <v>4.618848557</v>
+        <v>4.574055684</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4737667834096813</v>
+        <v>0.5255392466022221</v>
       </c>
       <c r="T93">
-        <v>7.838361933874673</v>
+        <v>8.786592778984131</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.059540749992689</v>
+        <v>2.037154437492768</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09295041972817775</v>
+        <v>0.09290788894948418</v>
       </c>
       <c r="C94">
-        <v>8.516956047545037</v>
+        <v>7.733547312995881</v>
       </c>
       <c r="D94">
-        <v>67.29095604754504</v>
+        <v>67.31704731299588</v>
       </c>
       <c r="E94">
-        <v>71.024</v>
+        <v>71.8335</v>
       </c>
       <c r="F94">
-        <v>74.474</v>
+        <v>75.2835</v>
       </c>
       <c r="G94">
         <v>15.7</v>
@@ -8995,28 +8995,28 @@
         <v>11.5</v>
       </c>
       <c r="M94">
-        <v>5.6451292</v>
+        <v>5.7064893</v>
       </c>
       <c r="N94">
-        <v>5.8548708</v>
+        <v>5.7935107</v>
       </c>
       <c r="O94">
-        <v>1.580815116</v>
+        <v>1.564247889</v>
       </c>
       <c r="P94">
-        <v>4.274055683999999</v>
+        <v>4.229262811</v>
       </c>
       <c r="Q94">
-        <v>4.574055684</v>
+        <v>4.529262811000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5255392466022221</v>
+        <v>0.5921038421354886</v>
       </c>
       <c r="T94">
-        <v>8.786592778984131</v>
+        <v>10.00574672269629</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.037154437492768</v>
+        <v>2.015249551068115</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09290788894948418</v>
+        <v>0.1026093981707906</v>
       </c>
       <c r="C95">
-        <v>7.733547312995881</v>
+        <v>1.453977242063928</v>
       </c>
       <c r="D95">
-        <v>67.31704731299588</v>
+        <v>61.84697724206394</v>
       </c>
       <c r="E95">
-        <v>71.8335</v>
+        <v>72.643</v>
       </c>
       <c r="F95">
-        <v>75.2835</v>
+        <v>76.093</v>
       </c>
       <c r="G95">
         <v>15.7</v>
@@ -9077,45 +9077,45 @@
         <v>11.5</v>
       </c>
       <c r="M95">
-        <v>5.7064893</v>
+        <v>6.84837</v>
       </c>
       <c r="N95">
-        <v>5.7935107</v>
+        <v>4.65163</v>
       </c>
       <c r="O95">
-        <v>1.564247889</v>
+        <v>1.2559401</v>
       </c>
       <c r="P95">
-        <v>4.229262811</v>
+        <v>3.3956899</v>
       </c>
       <c r="Q95">
-        <v>4.529262811000001</v>
+        <v>3.695689900000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5921038421354886</v>
+        <v>0.6808566361798443</v>
       </c>
       <c r="T95">
-        <v>10.00574672269629</v>
+        <v>11.63128531431251</v>
       </c>
       <c r="U95">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V95">
         <v>0.27</v>
       </c>
       <c r="W95">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y95">
-        <v>2.015249551068115</v>
+        <v>1.67923170039002</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1026093981707906</v>
+        <v>0.1026705273920971</v>
       </c>
       <c r="C96">
-        <v>1.453977242063928</v>
+        <v>0.6128272528301295</v>
       </c>
       <c r="D96">
-        <v>61.84697724206394</v>
+        <v>61.81532725283014</v>
       </c>
       <c r="E96">
-        <v>72.643</v>
+        <v>73.4525</v>
       </c>
       <c r="F96">
-        <v>76.093</v>
+        <v>76.9025</v>
       </c>
       <c r="G96">
         <v>15.7</v>
@@ -9159,28 +9159,28 @@
         <v>11.5</v>
       </c>
       <c r="M96">
-        <v>6.84837</v>
+        <v>6.921225</v>
       </c>
       <c r="N96">
-        <v>4.65163</v>
+        <v>4.578775</v>
       </c>
       <c r="O96">
-        <v>1.2559401</v>
+        <v>1.23626925</v>
       </c>
       <c r="P96">
-        <v>3.3956899</v>
+        <v>3.34250575</v>
       </c>
       <c r="Q96">
-        <v>3.695689900000001</v>
+        <v>3.642505750000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6808566361798443</v>
+        <v>0.8051105478419422</v>
       </c>
       <c r="T96">
-        <v>11.63128531431251</v>
+        <v>13.90703934257522</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.67923170039002</v>
+        <v>1.66155557722802</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1026705273920971</v>
+        <v>0.1027316566134035</v>
       </c>
       <c r="C97">
-        <v>0.6128272528301295</v>
+        <v>-0.2282903594146006</v>
       </c>
       <c r="D97">
-        <v>61.81532725283014</v>
+        <v>61.7837096405854</v>
       </c>
       <c r="E97">
-        <v>73.4525</v>
+        <v>74.262</v>
       </c>
       <c r="F97">
-        <v>76.9025</v>
+        <v>77.712</v>
       </c>
       <c r="G97">
         <v>15.7</v>
@@ -9241,28 +9241,28 @@
         <v>11.5</v>
       </c>
       <c r="M97">
-        <v>6.921225</v>
+        <v>6.99408</v>
       </c>
       <c r="N97">
-        <v>4.578775</v>
+        <v>4.50592</v>
       </c>
       <c r="O97">
-        <v>1.23626925</v>
+        <v>1.2165984</v>
       </c>
       <c r="P97">
-        <v>3.34250575</v>
+        <v>3.2893216</v>
       </c>
       <c r="Q97">
-        <v>3.642505750000001</v>
+        <v>3.5893216</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8051105478419422</v>
+        <v>0.9914914153350892</v>
       </c>
       <c r="T97">
-        <v>13.90703934257522</v>
+        <v>17.32067038496927</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.66155557722802</v>
+        <v>1.644247706631894</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1027316566134035</v>
+        <v>0.1027927858347099</v>
       </c>
       <c r="C98">
-        <v>-0.2282903594146006</v>
+        <v>-1.069375644325916</v>
       </c>
       <c r="D98">
-        <v>61.7837096405854</v>
+        <v>61.75212435567409</v>
       </c>
       <c r="E98">
-        <v>74.262</v>
+        <v>75.0715</v>
       </c>
       <c r="F98">
-        <v>77.712</v>
+        <v>78.5215</v>
       </c>
       <c r="G98">
         <v>15.7</v>
@@ -9323,28 +9323,28 @@
         <v>11.5</v>
       </c>
       <c r="M98">
-        <v>6.99408</v>
+        <v>7.066935</v>
       </c>
       <c r="N98">
-        <v>4.50592</v>
+        <v>4.433065</v>
       </c>
       <c r="O98">
-        <v>1.2165984</v>
+        <v>1.19692755</v>
       </c>
       <c r="P98">
-        <v>3.2893216</v>
+        <v>3.23613745</v>
       </c>
       <c r="Q98">
-        <v>3.5893216</v>
+        <v>3.536137450000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9914914153350869</v>
+        <v>1.30212619449033</v>
       </c>
       <c r="T98">
-        <v>17.32067038496923</v>
+        <v>23.01005545562597</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.644247706631894</v>
+        <v>1.627296699347029</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1027927858347099</v>
+        <v>0.1028539150560164</v>
       </c>
       <c r="C99">
-        <v>-1.069375644325916</v>
+        <v>-1.910428651457934</v>
       </c>
       <c r="D99">
-        <v>61.75212435567409</v>
+        <v>61.72057134854207</v>
       </c>
       <c r="E99">
-        <v>75.0715</v>
+        <v>75.881</v>
       </c>
       <c r="F99">
-        <v>78.5215</v>
+        <v>79.331</v>
       </c>
       <c r="G99">
         <v>15.7</v>
@@ -9405,28 +9405,28 @@
         <v>11.5</v>
       </c>
       <c r="M99">
-        <v>7.066935</v>
+        <v>7.13979</v>
       </c>
       <c r="N99">
-        <v>4.433065</v>
+        <v>4.36021</v>
       </c>
       <c r="O99">
-        <v>1.19692755</v>
+        <v>1.1772567</v>
       </c>
       <c r="P99">
-        <v>3.23613745</v>
+        <v>3.1829533</v>
       </c>
       <c r="Q99">
-        <v>3.536137450000001</v>
+        <v>3.482953300000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.30212619449033</v>
+        <v>1.923395752800817</v>
       </c>
       <c r="T99">
-        <v>23.01005545562597</v>
+        <v>34.38882559693944</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.627296699347029</v>
+        <v>1.610691630986345</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1028539150560164</v>
+        <v>0.1029150442773228</v>
       </c>
       <c r="C100">
-        <v>-1.910428651457934</v>
+        <v>-2.751449430263591</v>
       </c>
       <c r="D100">
-        <v>61.72057134854207</v>
+        <v>61.68905056973641</v>
       </c>
       <c r="E100">
-        <v>75.881</v>
+        <v>76.6905</v>
       </c>
       <c r="F100">
-        <v>79.331</v>
+        <v>80.1405</v>
       </c>
       <c r="G100">
         <v>15.7</v>
@@ -9487,28 +9487,28 @@
         <v>11.5</v>
       </c>
       <c r="M100">
-        <v>7.13979</v>
+        <v>7.212645</v>
       </c>
       <c r="N100">
-        <v>4.36021</v>
+        <v>4.287355</v>
       </c>
       <c r="O100">
-        <v>1.1772567</v>
+        <v>1.15758585</v>
       </c>
       <c r="P100">
-        <v>3.1829533</v>
+        <v>3.12976915</v>
       </c>
       <c r="Q100">
-        <v>3.482953300000001</v>
+        <v>3.42976915</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.923395752800817</v>
+        <v>3.787204427732279</v>
       </c>
       <c r="T100">
-        <v>34.38882559693944</v>
+        <v>68.52513602087988</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.610691630986345</v>
+        <v>1.59442201855214</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1029150442773228</v>
-      </c>
-      <c r="C101">
-        <v>-2.751449430263591</v>
-      </c>
-      <c r="D101">
-        <v>61.68905056973641</v>
-      </c>
-      <c r="E101">
-        <v>76.6905</v>
-      </c>
-      <c r="F101">
-        <v>80.1405</v>
-      </c>
-      <c r="G101">
-        <v>15.7</v>
-      </c>
-      <c r="H101">
-        <v>77.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>11.8</v>
-      </c>
-      <c r="K101">
-        <v>0.3000000000000007</v>
-      </c>
-      <c r="L101">
-        <v>11.5</v>
-      </c>
-      <c r="M101">
-        <v>7.212645</v>
-      </c>
-      <c r="N101">
-        <v>4.287355</v>
-      </c>
-      <c r="O101">
-        <v>1.15758585</v>
-      </c>
-      <c r="P101">
-        <v>3.12976915</v>
-      </c>
-      <c r="Q101">
-        <v>3.42976915</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.787204427732279</v>
-      </c>
-      <c r="T101">
-        <v>68.52513602087988</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.06569999999999999</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.59442201855214</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
